--- a/data_extactor/batch/501_550.xlsx
+++ b/data_extactor/batch/501_550.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0676FCC4-4F31-452F-901A-4C5BA0EF710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1651 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="546">
+  <si>
+    <t>29-2099.05</t>
+  </si>
+  <si>
+    <t>Ophthalmic Medical Technologists</t>
+  </si>
+  <si>
+    <t>Certified Diagnostic Ophthalmic Sonographer (CDOS) | Certified Ophthalmic Medical Technologist (COMT) | Ophthalmic Echographer | Ophthalmic Medical Technologist (Ophthalmic Medical Tech) | Ophthalmic Photographer | Ophthalmic Sonographer | Ophthalmic Technologist (Ophthalmic Tech) | Ophthalmic Ultrasonographer | Registered Ophthalmic Ultrasound Biometrist (ROUB) | Surgical Coordinator</t>
+  </si>
+  <si>
+    <t>AcuityPro | Autodesk AutoCAD | Computer aided design and drafting CADD software | Email software | EyeMD EMR Healthcare Systems EyeMD EMR | Hypertext preprocessor PHP | JavaScript | Medflow Complete | MediPro Medisoft Clinical | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | NaviNet Open | SAP software | Web browser software | ezChartWriter | iChartPlus</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension | Writing | Monitoring | Learning Strategies | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Medicine and Dentistry | English Language | Education and Training | Mathematics | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Expression | Near Vision | Oral Comprehension | Problem Sensitivity | Speech Recognition | Speech Clarity | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Finger Dexterity | Selective Attention | Flexibility of Closure | Arm-Hand Steadiness | Perceptual Speed | Category Flexibility | Information Ordering | Far Vision</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Physical Proximity | Importance of Being Exact or Accurate | Frequency of Decision Making | Exposed to Disease or Infections | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Anesthesiologist Assistants | Cardiologists | Cardiovascular Technologists and Technicians | Dermatologists | Diagnostic Medical Sonographers | Endoscopy Technicians | Magnetic Resonance Imaging Technologists | Medical Assistants | Medical and Clinical Laboratory Technologists | Neurodiagnostic Technologists | Ophthalmic Medical Technicians | Ophthalmologists, Except Pediatric | Optometrists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Radiation Therapists | Radiologic Technologists and Technicians | Radiologists | Surgical Assistants | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Assist ophthalmologists by performing ophthalmic clinical functions and ophthalmic photography. Provide instruction and supervision to other ophthalmic personnel. Assist with minor surgical procedures, applying aseptic techniques and preparing instruments. May perform eye exams, administer eye medications, and instruct patients in care and use of corrective lenses.</t>
+  </si>
+  <si>
+    <t>Administer topical ophthalmic or oral medications. | Assess abnormalities of color vision, such as amblyopia. | Assess refractive condition of eyes, using retinoscope. | Assist physicians in performing ophthalmic procedures, including surgery. | Calculate corrections for refractive errors. | Call patients to inquire about their post-operative status or recovery. | Clean or sterilize ophthalmic or surgical instruments. | Collect ophthalmic measurements or other diagnostic information, using ultrasound equipment, such as A-scan ultrasound biometry or B-scan ultrasonography equipment. | Conduct binocular disparity tests to assess depth perception. | Conduct low vision blindness tests. | Conduct ocular motility tests to measure function of eye muscles. | Conduct tests, such as the Amsler Grid test, to measure central visual field used in the early diagnosis of macular degeneration, glaucoma, or diseases of the eye. | Conduct tonometry or tonography tests to measure intraocular pressure. | Conduct visual field tests to measure field of vision. | Create three-dimensional images of the eye, using computed tomography (CT). | Educate patients on ophthalmic medical procedures, conditions of the eye, and appropriate use of medications. | Instruct patients in the care and use of contact lenses. | Maintain ophthalmic instruments or equipment. | Measure and record lens power, using lensometers. | Measure corneal curvature with keratometers or ophthalmometers to aid in the diagnosis of conditions, such as astigmatism. | Measure corneal thickness, using pachymeter or contact ultrasound methods. | Measure the thickness of the retinal nerve, using scanning laser polarimetry techniques to aid in diagnosis of glaucoma. | Measure visual acuity, including near, distance, pinhole, or dynamic visual acuity, using appropriate tests. | Perform advanced ophthalmic procedures, including electrophysiological, electrophysical, or microbial procedures. | Perform fluorescein angiography of the eye. | Perform ophthalmic triage, in the office or by phone, to assess severity of patients' conditions. | Perform slit lamp biomicroscopy procedures to diagnose disorders of the eye, such as retinitis, presbyopia, cataracts, or retinal detachment. | Photograph patients' eye areas, using clinical photography techniques, to document retinal or corneal defects. | Supervise or instruct ophthalmic staff. | Take anatomical or functional ocular measurements, such as axial length measurements, of the eye or surrounding tissue. | Take and document patients' medical histories.</t>
+  </si>
+  <si>
+    <t>29-2099.08</t>
+  </si>
+  <si>
+    <t>Patient Representatives</t>
+  </si>
+  <si>
+    <t>Access Representative | Admissions Coordinator | Case Manager | Medicaid Service Coordinator (MSC) | Patient Access Coordinator | Patient Access Specialist | Patient Advocate | Patient Navigator | Patient Resource Worker | Patient Service Representative</t>
+  </si>
+  <si>
+    <t>Admissions, discharge, and transfer ADT software | CareOne CareEnsure | Complaint management software | Corel WordPerfect Office Suite | Customer Expressions i-Sight | Data entry software | Database software | Electronic medical record EMR software | Epic EpicCare Inpatient Clinical System | Epic Systems | Epic Systems software | FaceTime | Google Docs | Healthcare common procedure coding system HCPCS | Henry Schein Dentrix | IBM Notes | MEDITECH software | Manhattan Cross Cultural Group Quality Interactions | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Patient satisfaction assessment software | Pemimic Patient Relations Suite | Peminic Patient Safety &amp; Quality Suite | PracticeWorks Systems Kodak WINOMS CS | Prognosis Solutions ResolvPRM | Scheduling software | Web browser software | eClinicalWorks EHR software | rL Solutions Feedback MonitorPro</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Speaking | Critical Thinking | Active Learning | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Medicine and Dentistry | Sociology and Anthropology | Administrative | Psychology | Administration and Management | Computers and Electronics | English Language | Education and Training | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Speech Clarity | Problem Sensitivity | Information Ordering | Selective Attention | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Contact With Others | E-Mail | Telephone Conversations | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Freedom to Make Decisions | Spend Time Sitting | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Disease or Infections | Conflict Situations | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Child, Family, and School Social Workers | Clinical Nurse Specialists | Community Health Workers | Eligibility Interviewers, Government Programs | Health Education Specialists | Health Informatics Specialists | Health Information Technologists and Medical Registrars | Healthcare Social Workers | Medical Assistants | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Medical and Health Services Managers | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Nursing Assistants | Psychiatric Technicians | Registered Nurses | Rehabilitation Counselors | Social and Human Service Assistants</t>
+  </si>
+  <si>
+    <t>Assist patients in obtaining services, understanding policies and making health care decisions.</t>
+  </si>
+  <si>
+    <t>Analyze patients' abilities to pay to determine charges on a sliding scale. | Collect and report data on topics, such as patient encounters or inter-institutional problems, making recommendations for change when appropriate. | Coordinate communication between patients, family members, medical staff, administrative staff, or regulatory agencies. | Develop and distribute newsletters, brochures, or other printed materials to share information with patients or medical staff. | Explain policies, procedures, or services to patients using medical or administrative knowledge. | Identify and share research, recommendations, or other information regarding legal liabilities, risk management, or quality of care. | Interview patients or their representatives to identify problems relating to care. | Investigate and direct patient inquiries or complaints to appropriate medical staff members and follow up to ensure satisfactory resolution. | Maintain knowledge of community services and resources available to patients. | Provide consultation or training to volunteers or staff on topics, such as guest relations, patients' rights, or medical issues. | Read current literature, talk with colleagues, continue education, or participate in professional organizations or conferences to keep abreast of developments in the field. | Refer patients to appropriate health care services or resources. | Teach patients to use home health care equipment.</t>
+  </si>
+  <si>
+    <t>29-9021.00</t>
+  </si>
+  <si>
+    <t>Health Information Technologists and Medical Registrars</t>
+  </si>
+  <si>
+    <t>Medical Records Analyst | Medical Records Director</t>
+  </si>
+  <si>
+    <t>3M Encoder | Allscripts EHR | Amazing Charts | American Medical Association CodeManager | Azalea Health Azalea EHR | Billing software | Coding database software | ComChart EMR | Computerized indexing systems | Corel WordPerfect Office Suite | Cyber Records MediChart Express | DRG grouping software | Digital Imaging Communications in Medicine DICOM medical imaging software | EHS CareRevolution | Eko | Electronic medical record EMR software | Electronic medical record EMR systems | Elekta METRIQ | Email software | Encoded archival system EAD | Encoder software | EndoSoft | Entity Management Software | Epic Systems | Fox Meadows Accent Data Manager | Fox Meadows ChartingPlus | Fox Meadows EncounterManager | GE Healthcare Logician | Graphics software | Greenway Medical Technologies PrimeChart | HMS | Health Care Data HealthProbe | Healthcare common procedure coding system HCPCS | Henry Schein Dentrix | Holt Systems eMedRec | Hyland Software OnBase | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Lotus 1-2-3 | IBM SPSS Statistics | IDX Systems IDXtend | IDX Systems Patient Chart Tracking | Information Resource Products Clinical Coding Expert | Laserfiche software | LeonardoMD Renaissance | MD Synergy Medical Appointment Scheduling | MEDITECH software | MedStar Systems DrWorks | Mediasoft mediOFFICE | MedicWare EMR | Medical condition coding software | Medical procedure coding software | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Word | Minitab | NCG Medical Systems d-Chart | NDCMedisoft | NextGen Healthcare Information Systems EMR | PCC EHR | PCC Pediatric Partner | PowerMed | Practice Partner Patient Records | Purkinje Dossier | QMSoftware Receivables Management | Qlik Tech QlikView | Quest Erwin Data Modeler | R | SAP Business Objects | SAP Crystal Reports | SAS | SOAPware EMR | STAT! Systems QD Clinical | ScanSoft Naturally Speaking | Scantron imaging software | Scheduling software | Siemens Soarian Financials | Siemens Soarian Scheduling | SoftMed ChartLocater | SoftMed ChartRelease | SoftMed ChartReserve | Speech recognition software | StataCorp Stata | Structured query language SQL | SynaMed EMR | Tableau | Teradata Database | VantageMed ChartKeeper | Virtual private networking VPN software | Visionary Medical Systems Visionary OFFICE PM | Voice dictation software | Web browser software | Welford Chart Notes | e-MDs topsChart | eClinicalWorks EHR software | eMDs Practice Partner</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Medicine and Dentistry | English Language | Administration and Management | Customer and Personal Service | Mathematics | Law and Government | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Bioinformatics Technicians | Clinical Data Managers | Clinical Nurse Specialists | Clinical Research Coordinators | Computer Systems Analysts | Database Administrators | Database Architects | Document Management Specialists | Genetic Counselors | Health Informatics Specialists | Human Resources Assistants, Except Payroll and Timekeeping | Management Analysts | Medical Records Specialists | Medical and Health Services Managers | Operations Research Analysts | Patient Representatives | Preventive Medicine Physicians | Regulatory Affairs Specialists | Statistical Assistants</t>
+  </si>
+  <si>
+    <t>Apply knowledge of healthcare and information systems to assist in the design, development, and continued modification and analysis of computerized healthcare systems. Abstract, collect, and analyze treatment and followup information of patients. May educate staff and assist in problem solving to promote the implementation of the healthcare information system. May design, develop, test, and implement databases with complete history, diagnosis, treatment, and health status to help monitor diseases.</t>
+  </si>
+  <si>
+    <t>Assign the patient to diagnosis-related groups (DRGs), using appropriate computer software. | Compile medical care and census data for statistical reports on diseases treated, surgery performed, or use of hospital beds. | Design databases to support healthcare applications, ensuring security, performance and reliability. | Develop in-service educational materials. | Evaluate and recommend upgrades or improvements to existing computerized healthcare systems. | Facilitate and promote activities, such as lunches, seminars, or tours, to foster healthcare information privacy or security awareness within the organization. | Identify, compile, abstract, and code patient data, using standard classification systems. | Manage the department or supervise clerical workers, directing or controlling activities of personnel in the medical records department. | Monitor changes in legislation and accreditation standards that affect information security or privacy in the computerized healthcare system. | Plan, develop, maintain, or operate a variety of health record indexes or storage and retrieval systems to collect, classify, store, or analyze information. | Prepare statistical reports, narrative reports, or graphic presentations of information, such as tumor registry data for use by hospital staff, researchers, or other users. | Protect the security of medical records to ensure that confidentiality is maintained. | Resolve or clarify codes or diagnoses with conflicting, missing, or unclear information by consulting with doctors or others or by participating in the coding team's regular meetings. | Retrieve patient medical records for physicians, technicians, or other medical personnel. | Train medical records staff. | Write or maintain archived procedures, procedural codes, or queries for applications.</t>
+  </si>
+  <si>
+    <t>29-9091.00</t>
+  </si>
+  <si>
+    <t>Athletic Trainers</t>
+  </si>
+  <si>
+    <t>Athletic Instructor | Athletic Lecturer | Athletic Trainer | Certified Athletic Trainer | Personal Trainer | Resident Athletic Trainer | Women's Athletic Trainer</t>
+  </si>
+  <si>
+    <t>BioEx Systems Exercise Pro | Database software | Digital Coach AthleticTrainer | Email software | ImPACT Applications ImPACT | Injury tracking software | Keffer Development Services Athletic Trainer System ATS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Premier Software Simtrak Mobility | Scheduling software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Speaking | Critical Thinking | Reading Comprehension | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Customer and Personal Service | Psychology | Therapy and Counseling | English Language | Education and Training | Public Safety and Security | Administrative | Biology | Administration and Management</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Expression | Speech Clarity | Written Comprehension | Speech Recognition | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Oral Comprehension | Near Vision | Multilimb Coordination | Flexibility of Closure | Originality | Fluency of Ideas | Arm-Hand Steadiness | Selective Attention | Category Flexibility | Far Vision | Static Strength | Finger Dexterity | Manual Dexterity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | E-Mail | Frequency of Decision Making | Indoors, Environmentally Controlled | Freedom to Make Decisions | Health and Safety of Other Workers | Telephone Conversations | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Outdoors, Exposed to All Weather Conditions | Physical Proximity | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Written Letters and Memos | Consequence of Error | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Disease or Infections | Level of Competition | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Repeating Same Tasks | Spend Time Standing | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Chiropractors | Coaches and Scouts | Exercise Physiologists | Exercise Trainers and Group Fitness Instructors | Fitness and Wellness Coordinators | Nurse Practitioners | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Orthotists and Prosthetists | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Psychiatric Technicians | Recreational Therapists | Registered Nurses | Respiratory Therapists | Sports Medicine Physicians | Training and Development Specialists</t>
+  </si>
+  <si>
+    <t>Evaluate and treat musculoskeletal injuries or illnesses. Provide preventive, therapeutic, emergency, and rehabilitative care.</t>
+  </si>
+  <si>
+    <t>Accompany injured athletes to hospitals. | Advise athletes on the proper use of equipment. | Apply protective or injury preventive devices, such as tape, bandages, or braces, to body parts, such as ankles, fingers, or wrists. | Assess and report the progress of recovering athletes to coaches or physicians. | Care for athletic injuries, using physical therapy equipment, techniques, or medication. | Clean and sanitize athletic training rooms. | Collaborate with physicians to develop and implement comprehensive rehabilitation programs for athletic injuries. | Conduct an initial assessment of an athlete's injury or illness to provide emergency or continued care and to determine whether they should be referred to physicians for definitive diagnosis and treatment. | Conduct research or provide instruction on subject matter related to athletic training or sports medicine. | Confer with coaches to select protective equipment. | Develop training programs or routines designed to improve athletic performance. | Evaluate athletes' readiness to play and provide participation clearances when necessary and warranted. | File athlete insurance claims and communicate with insurance providers. | Inspect playing fields to locate any items that could injure players. | Instruct coaches, athletes, parents, medical personnel, or community members in the care and prevention of athletic injuries. | Lead stretching exercises for team members prior to games or practices. | Massage body parts to relieve soreness, strains, or bruises. | Perform general administrative tasks, such as keeping records or writing reports. | Perform team support duties, such as running errands, maintaining equipment, or stocking supplies. | Plan or implement comprehensive athletic injury or illness prevention programs. | Recommend special diets to improve athletes' health, increase their stamina, or alter their weight. | Teach sports medicine courses to athletic training students. | Travel with athletic teams to be available at sporting events.</t>
+  </si>
+  <si>
+    <t>29-9092.00</t>
+  </si>
+  <si>
+    <t>Genetic Counselors</t>
+  </si>
+  <si>
+    <t>Certified Genetic Counselor | Genetic Counselor | Medical Science Liaison | Prenatal and Pediatric Genetic Counselor | Reproductive Genetic Counseling Coordinator</t>
+  </si>
+  <si>
+    <t>BRCAPRO | Benetech PRA | Breast Cancer Risk Assessment Tool | CancerGene | CyrillicSoftware Cyrillic | Database software | FileMaker Pro | Ftree | Jurek Software Pedigree-Draw | Medgen PED | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | PedHunter | PediDraw | Pedigree drawing and management software | Progeny Software Progeny Clinical | Prognosis Innovation Healthcare ChartAccess | SynDiag | Wageningen MapChart | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Writing | Speaking | Critical Thinking | Active Learning | Science | Monitoring | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Biology | Psychology | Medicine and Dentistry | Therapy and Counseling | English Language | Customer and Personal Service | Mathematics | Sociology and Anthropology | Education and Training</t>
+  </si>
+  <si>
+    <t>Written Comprehension | Deductive Reasoning | Oral Comprehension | Oral Expression | Written Expression | Problem Sensitivity | Inductive Reasoning | Information Ordering | Speech Recognition | Speech Clarity | Near Vision | Flexibility of Closure | Mathematical Reasoning | Category Flexibility | Originality | Fluency of Ideas | Selective Attention</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Telephone Conversations | Written Letters and Memos | Contact With Others | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Spend Time Sitting | Deal With External Customers or the Public in General | Frequency of Decision Making | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Time Pressure | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Advanced Practice Psychiatric Nurses | Allergists and Immunologists | Cardiologists | Clinical Neuropsychologists | Clinical Nurse Specialists | Clinical and Counseling Psychologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Neurologists | Nurse Midwives | Nurse Practitioners | Obstetricians and Gynecologists | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Preventive Medicine Physicians | Psychiatric Technicians | Psychiatrists</t>
+  </si>
+  <si>
+    <t>Assess individual or family risk for a variety of inherited conditions, such as genetic disorders and birth defects. Provide information to other healthcare providers or to individuals and families concerned with the risk of inherited conditions. Advise individuals and families to support informed decisionmaking and coping methods for those at risk. May help conduct research related to genetic conditions or genetic counseling.</t>
+  </si>
+  <si>
+    <t>Analyze genetic information to identify patients or families at risk for specific disorders or syndromes. | Assess patients' psychological or emotional needs, such as those relating to stress, fear of test results, financial issues, and marital conflicts to make referral recommendations or assist patients in managing test outcomes. | Collect for, or share with, research projects patient data on specific genetic disorders or syndromes. | Design and conduct genetics training programs for physicians, graduate students, other health professions or the general community. | Determine or coordinate treatment plans by requesting laboratory services, reviewing genetics or counseling literature, and considering histories or diagnostic data. | Discuss testing options and the associated risks, benefits and limitations with patients and families to assist them in making informed decisions. | Engage in research activities related to the field of medical genetics or genetic counseling. | Evaluate or make recommendations for standards of care or clinical operations, ensuring compliance with applicable regulations, ethics, legislation, or policies. | Explain diagnostic procedures such as chorionic villus sampling (CVS), ultrasound, fetal blood sampling, and amniocentesis. | Identify funding sources and write grant proposals for eligible programs or services. | Interpret laboratory results and communicate findings to patients or physicians. | Interview patients or review medical records to obtain comprehensive patient or family medical histories, and document findings. | Prepare or provide genetics-related educational materials to patients or medical personnel. | Provide counseling to patient and family members by providing information, education, or reassurance. | Provide genetic counseling in specified areas of clinical genetics, such as obstetrics, pediatrics, oncology and neurology. | Provide patients with information about the inheritance of conditions such as cardiovascular disease, Alzheimer's disease, diabetes, and various forms of cancer. | Read current literature, talk with colleagues, or participate in professional organizations or conferences to keep abreast of developments in genetics. | Refer patients to specialists or community resources. | Write detailed consultation reports to provide information on complex genetic concepts to patients or referring physicians.</t>
+  </si>
+  <si>
+    <t>29-9093.00</t>
+  </si>
+  <si>
+    <t>Surgical Assistants</t>
+  </si>
+  <si>
+    <t>Certified First Assistant (CFA) | Certified Registered Nurse First Assistant (CRNFA) | Certified Surgical Assistant (CSA) | Certified Surgical First Assistant (CSFA) | Certified Surgical Technician | Gastrointestinal Technician (GI Technician) | Registered Nurse First Assistant (RNFA) | Surgical First Assistant | Surgical Scrub Technician (Surgical Scrub Tech) | Surgical Technician (Surgical Tech)</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | MEDITECH software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Nursing documentation software | Patient scheduling software | Patient tracking software | Supply documentation software | Surgery workflow communication software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing | Learning Strategies | Active Learning</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Customer and Personal Service | English Language | Biology | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Arm-Hand Steadiness | Finger Dexterity | Near Vision | Problem Sensitivity | Speech Clarity | Oral Expression | Written Comprehension | Visual Color Discrimination | Speech Recognition | Control Precision | Information Ordering | Manual Dexterity | Selective Attention | Inductive Reasoning | Deductive Reasoning | Perceptual Speed | Multilimb Coordination | Hearing Sensitivity | Written Expression | Flexibility of Closure | Auditory Attention | Trunk Strength | Reaction Time | Visualization | Category Flexibility | Speed of Closure | Memorization | Wrist-Finger Speed | Time Sharing | Far Vision | Static Strength</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Physical Proximity | Contact With Others | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Disease or Infections | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Consequence of Error | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Exposed to Hazardous Conditions | Exposed to Contaminants | Telephone Conversations | Importance of Repeating Same Tasks | Frequency of Decision Making | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to Radiation | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Cardiovascular Technologists and Technicians | Critical Care Nurses | Emergency Medical Technicians | Emergency Medicine Physicians | Endoscopy Technicians | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Nurse Anesthetists | Nursing Assistants | Ophthalmic Medical Technicians | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Physician Assistants | Respiratory Therapists | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Assist in operations, under the supervision of surgeons. May, in accordance with state laws, help surgeons to make incisions and close surgical sites, manipulate or remove tissues, implant surgical devices or drains, suction the surgical site, place catheters, clamp or cauterize vessels or tissue, and apply dressings to surgical site.</t>
+  </si>
+  <si>
+    <t>Adjust and maintain operating room temperature, humidity, or lighting, according to surgeon's specifications. | Apply sutures, staples, clips, or other materials to close skin, facia, or subcutaneous wound layers. | Assess skin integrity or other body conditions upon completion of the procedure to determine if damage has occurred from body positioning. | Assist in applying casts, splints, braces, or similar devices. | Assist in the insertion, positioning, or suturing of closed-wound drainage systems. | Assist in volume replacement or autotransfusion techniques. | Assist members of surgical team with gowning or gloving. | Assist with patient resuscitation during cardiac arrest or other life-threatening events. | Clamp, ligate, or cauterize blood vessels to control bleeding during surgical entry, using hemostatic clamps, suture ligatures, or electrocautery equipment. | Coordinate or participate in the positioning of patients, using body stabilizing equipment or protective padding to provide appropriate exposure for the procedure or to protect against nerve damage or circulation impairment. | Coordinate with anesthesia personnel to maintain patient temperature. | Cover patients with surgical drapes to create and maintain a sterile operative field. | Determine availability of necessary equipment or supplies for operative procedures. | Discuss with surgeon the nature of the surgical procedure, including operative consent, methods of operative exposure, diagnostic or laboratory data, or patient-advanced directives or other needs. | Gather, arrange, or assemble instruments or supplies. | Incise tissue layers in lower extremities to harvest veins. | Insert or remove urinary bladder catheters. | Maintain an unobstructed operative field, using surgical retractors, sponges, or suctioning and irrigating equipment. | Monitor and maintain aseptic technique throughout procedures. | Monitor patient intra-operative status, including patient position, vital signs, or volume and color of blood. | Obtain or inspect sterile or non-sterile surgical equipment, instruments, or supplies. | Operate sterilizing devices. | Pass instruments or supplies to surgeon during procedure. | Postoperatively inject a subcutaneous local anesthetic agent to reduce pain. | Prepare and apply sterile wound dressings. | Remove patient hair or disinfect incision sites to prepare patient for surgery. | Transport patients to operating room. | Verify the identity of patient or operative site.</t>
+  </si>
+  <si>
+    <t>29-9099.00</t>
+  </si>
+  <si>
+    <t>Healthcare Practitioners and Technical Workers, All Other</t>
+  </si>
+  <si>
+    <t>Clinical Coordinator | Clinical Documentation Specialist | Health Practitioner | Healthcare Specialist | Infection Preventionist | Medical Coder | Patient Care Coordinator | Quality Improvement Specialist | Utilization Review Specialist | Clinical Informatics Specialist</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Critical Thinking | Speaking | Science | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Customer and Personal Service | English Language | Computers and Electronics | Administration and Management | Biology | Law and Government | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Health Information Technologists and Medical Registrars | Medical Records Specialists | Patient Representatives | Genetic Counselors | Athletic Trainers | Surgical Assistants | Orthotists and Prosthetists | Hearing Aid Specialists | Opticians, Dispensing | Registered Nurses | Licensed Practical and Licensed Vocational Nurses | Physician Assistants | Health Technologists and Technicians, All Other | Healthcare Diagnosing or Treating Practitioners, All Other | Medical and Health Services Managers | Health Education Specialists | Healthcare Social Workers | Clinical Research Coordinators | Epidemiologists | Health Specialties Teachers, Postsecondary</t>
+  </si>
+  <si>
+    <t>All healthcare practitioners and technical workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform healthcare practitioner and technical duties not classified separately. | Review clinical documentation for accuracy, completeness, and compliance. | Coordinate patient care activities among providers, departments, and facilities. | Analyze clinical data to support quality improvement and reporting requirements. | Educate clinical staff on documentation, coding, and regulatory standards. | Monitor compliance with accreditation, licensing, and safety requirements. | Investigate incidents, infections, or quality concerns and recommend corrective actions. | Prepare reports and dashboards for clinical leadership and regulatory bodies. | Maintain registries, databases, and clinical information systems. | Communicate with patients and families to resolve concerns and coordinate services. | Participate in policy development and clinical protocol revision. | Verify insurance authorization and medical necessity for services. | Support clinical research, audits, and data collection activities. | Maintain professional credentials through continuing education.</t>
+  </si>
+  <si>
+    <t>29-9099.01</t>
+  </si>
+  <si>
+    <t>Midwives</t>
+  </si>
+  <si>
+    <t>Birth Center Midwife | Certified Direct-Entry Midwife | Certified Professional Midwife (CPM) | Homebirth Midwife | Lay Midwife | Licensed Certified Professional Midwife | Licensed Direct Entry Midwife | Licensed Midwife (LM) | Licensed and Certified Midwife</t>
+  </si>
+  <si>
+    <t>AS/400 Database | Email software | Epic Systems | Extensible markup language XML | MEDITECH software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Patient electronic medical record EMR software | Private Practice | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Speaking | Reading Comprehension | Active Learning | Learning Strategies | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Medicine and Dentistry | Psychology | Therapy and Counseling | English Language | Biology | Education and Training | Sociology and Anthropology | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Speech Clarity | Speech Recognition | Near Vision | Information Ordering | Written Expression | Category Flexibility | Selective Attention | Flexibility of Closure | Fluency of Ideas | Arm-Hand Steadiness | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Physical Proximity | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Contact With Others | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Consequence of Error | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Disease or Infections | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Acupuncturists | Acute Care Nurses | Advanced Practice Psychiatric Nurses | Anesthesiologists | Clinical Nurse Specialists | Critical Care Nurses | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Licensed Practical and Licensed Vocational Nurses | Naturopathic Physicians | Nurse Anesthetists | Nurse Midwives | Nurse Practitioners | Obstetricians and Gynecologists | Paramedics | Pediatricians, General | Physician Assistants | Psychiatrists | Registered Nurses</t>
+  </si>
+  <si>
+    <t>Provide prenatal care and childbirth assistance.</t>
+  </si>
+  <si>
+    <t>Assess birthing environments to ensure cleanliness, safety, and the availability of appropriate supplies. | Assess the status of post-date pregnancies to determine treatments and interventions. | Assist maternal patients to find physical positions that will facilitate childbirth. | Collaborate in research studies. | Collect specimens for use in laboratory tests. | Compile and evaluate clinical practice statistics. | Complete birth certificates. | Conduct ongoing prenatal health assessments, tracking changes in physical and emotional health. | Counsel women regarding the nutritional requirements of pregnancy. | Develop, implement, or evaluate individualized plans for midwifery care. | Establish and follow emergency or contingency plans for mothers and newborns. | Estimate patients' due dates and re-evaluate as necessary based on examination results. | Evaluate patients' laboratory and medical records, requesting assistance from other practitioners when necessary. | Identify tubal and ectopic pregnancies and refer patients for treatments. | Identify, monitor, or treat pregnancy-related problems such as hypertension, gestational diabetes, pre-term labor, or retarded fetal growth. | Incorporate research findings into practice as appropriate. | Inform patients of how to prepare and supply birth sites. | Maintain documentation of all patients' contacts, reviewing and updating records as necessary. | Monitor fetal growth and well-being through heartbeat detection, body measurement, and palpation. | Monitor maternal condition during labor by checking vital signs, monitoring uterine contractions, or performing physical examinations. | Obtain complete health and medical histories from patients including medical, surgical, reproductive, or mental health histories. | Perform annual gynecologic exams, including pap smears and breast exams. | Perform post-partum health assessments of mothers and babies at regular intervals. | Provide comfort and relaxation measures for mothers in labor through interventions such as massage, breathing techniques, hydrotherapy, or music. | Provide information about community health and social resources. | Provide information about the physical and emotional processes involved in the pregnancy, labor, birth, and postpartum periods. | Provide necessary medical care for infants at birth, including emergency care such as resuscitation. | Provide patients with contraceptive and family planning information. | Provide, or refer patients to other providers for, education or counseling on topics such as genetic testing, newborn care, contraception, or breastfeeding. | Recommend the use of vitamin and mineral supplements to enhance the health of patients and children. | Refer patients to specialists for procedures such as ultrasounds or biophysical profiles. | Respond to breech birth presentations by applying methods such as exercises or external version. | Set up or monitor the administration of oxygen or medications. | Suture perineal lacerations. | Test patients' hemoglobin, hematocrit, and blood glucose levels. | Treat patients' symptoms with alternative health care methods such as herbs or hydrotherapy.</t>
+  </si>
+  <si>
+    <t>31-1121.00</t>
+  </si>
+  <si>
+    <t>Home Health Aides</t>
+  </si>
+  <si>
+    <t>Caregiver | Certified Home Health Aide (CHHA) | Certified Medical Aide (CMA) | Certified Nurses Aide (CNA) | Home Attendant | Home Care Aide | Home Health Aide (HHA) | Home Health Provider | Hospice Aide | In Home Caregiver</t>
+  </si>
+  <si>
+    <t>AIGHD OASIS | FaceTime | Linux | Mi-Co software | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Python | SAP software | Salesforce software | UNIX | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Reading Comprehension | Writing | Speaking | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Problem Sensitivity | Near Vision | Inductive Reasoning | Deductive Reasoning | Information Ordering | Speech Recognition | Speech Clarity | Written Expression | Fluency of Ideas | Written Comprehension | Far Vision | Arm-Hand Steadiness | Time Sharing | Selective Attention | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Contact With Others | Physical Proximity | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Consequence of Error | Determine Tasks, Priorities and Goals | Spend Time Standing | Health and Safety of Other Workers | Spend Time Bending or Twisting Your Body | Exposed to Disease or Infections</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Clinical Nurse Specialists | Emergency Medical Technicians | Emergency Medicine Physicians | Family Medicine Physicians | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Nurse Practitioners | Nursing Assistants | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Paramedics | Personal Care Aides | Physical Therapist Aides | Physical Therapist Assistants | Psychiatric Aides | Psychiatric Technicians | Recreational Therapists | Registered Nurses</t>
+  </si>
+  <si>
+    <t>Monitor the health status of an individual with disabilities or illness, and address their health-related needs, such as changing bandages, dressing wounds, or administering medication. Work is performed under the direction of offsite or intermittent onsite licensed nursing staff. Provide assistance with routine healthcare tasks or activities of daily living, such as feeding, bathing, toileting, or ambulation. May also help with tasks such as preparing meals, doing light housekeeping, and doing laundry depending on the patient's abilities.</t>
+  </si>
+  <si>
+    <t>Accompany clients to doctors' offices or on other trips outside the home, providing transportation, assistance, and companionship. | Administer prescribed oral medications, under the written direction of physician or as directed by home care nurse or aide, and ensure patients take their medicine. | Bathe patients. | Care for children with disabilities or who have sick parents or parents with disabilities. | Care for patients by changing bed linens, washing and ironing laundry, cleaning, or assisting with their personal care. | Change dressings. | Check patients' pulse, temperature, and respiration. | Direct patients in simple prescribed exercises or in the use of braces or artificial limbs. | Entertain, converse with, or read aloud to patients to keep them mentally healthy and alert. | Maintain records of patient care, condition, progress, or problems to report and discuss observations with supervisor or case manager. | Massage patients or apply preparations or treatments, such as liniment, alcohol rubs, or heat-lamp stimulation. | Perform a variety of duties as requested by client, such as obtaining household supplies or running errands. | Plan, purchase, prepare, or serve meals to patients or other family members, according to prescribed diets. | Provide patients and families with emotional support and instruction in areas such as caring for infants, preparing healthy meals, living independently, or adapting to disability or illness. | Provide patients with help moving in and out of beds, baths, wheelchairs, or automobiles and with dressing and grooming.</t>
+  </si>
+  <si>
+    <t>31-1122.00</t>
+  </si>
+  <si>
+    <t>Personal Care Aides</t>
+  </si>
+  <si>
+    <t>Care Provider | Caregiver | Direct Care Worker | Home Care Aide | Medication Aide | Personal Care Aide | Personal Care Assistant (PCA) | Personal Care Attendant (PCA) | Resident Assistant | Resident Care Assistant (RCA)</t>
+  </si>
+  <si>
+    <t>Appletree | August Systems Visit Wizard | Computer reading software | Email software | FaceTime | MEDITECH software | Mi-Co Mi-Forms | Voltage SecureMail</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>English Language | Transportation | Customer and Personal Service | Education and Training | Psychology | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Written Comprehension | Deductive Reasoning | Speech Clarity | Speech Recognition | Near Vision | Information Ordering | Inductive Reasoning | Written Expression | Trunk Strength | Selective Attention</t>
+  </si>
+  <si>
+    <t>Physical Proximity | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Disease or Infections | Time Pressure | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Consequence of Error | Telephone Conversations | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Childcare Workers | Community Health Workers | First-Line Supervisors of Personal Service Workers | Healthcare Social Workers | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Nannies | Nursing Assistants | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Therapist Aides | Psychiatric Aides | Psychiatric Technicians | Rehabilitation Counselors | Social and Community Service Managers | Social and Human Service Assistants</t>
+  </si>
+  <si>
+    <t>Provide personalized assistance to individuals with disabilities or illness who require help with personal care and activities of daily living support (e.g., feeding, bathing, dressing, grooming, toileting, and ambulation). May also provide help with tasks such as preparing meals, doing light housekeeping, and doing laundry. Work is performed in various settings depending on the needs of the care recipient and may include locations such as their home, place of work, out in the community, or at a daytime nonresidential facility.</t>
+  </si>
+  <si>
+    <t>Administer bedside or personal care, such as ambulation or personal hygiene assistance. | Care for individuals or families during periods of incapacitation, family disruption, or convalescence, providing companionship, personal care, or help in adjusting to new lifestyles. | Instruct or advise clients on issues, such as household cleanliness, utilities, hygiene, nutrition, or infant care. | Participate in case reviews, consulting with the team caring for the client, to evaluate the client's needs and plan for continuing services. | Perform healthcare-related tasks, such as monitoring vital signs and medication, under the direction of registered nurses or physiotherapists. | Perform housekeeping duties, such as cooking, cleaning, washing clothes or dishes, or running errands. | Plan, shop for, or prepare nutritious meals or assist families in planning, shopping for, or preparing nutritious meals. | Prepare and maintain records of client progress and services performed, reporting changes in client condition to manager or supervisor. | Provide clients with communication assistance, typing their correspondence or obtaining information for them. | Train family members to provide bedside care. | Transport clients to locations outside the home, such as to physicians' offices or on outings, using a motor vehicle.</t>
+  </si>
+  <si>
+    <t>31-1131.00</t>
+  </si>
+  <si>
+    <t>Nursing Assistants</t>
+  </si>
+  <si>
+    <t>Certified Medication Aide (CMA) | Certified Nurse Aide (CNA) | Certified Nurses Aide (CNA) | Certified Nursing Assistant (CNA) | Licensed Nursing Assistant (LNA) | Nurses' Aide | Nursing Aide | Nursing Assistant | Patient Care Assistant (PCA) | State Tested Nursing Assistant (STNA)</t>
+  </si>
+  <si>
+    <t>Apache Spark | Billing software | Epic Systems | FaceTime | GE Healthcare Centricity EMR | Health information database software | MEDITECH software | Medical condition coding software | Medical procedure coding software | Medical record charting software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | PointClickCare healthcare software | Telemetry software | Web browser software | YouTube</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | English Language | Public Safety and Security | Medicine and Dentistry | Education and Training | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Near Vision | Speech Recognition | Static Strength | Trunk Strength | Information Ordering | Deductive Reasoning | Written Expression | Written Comprehension | Extent Flexibility | Arm-Hand Steadiness | Category Flexibility | Inductive Reasoning | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work With or Contribute to a Work Group or Team | Spend Time Walking or Running | Importance of Being Exact or Accurate | Spend Time Standing | Health and Safety of Other Workers | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Disease or Infections | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People | Indoors, Environmentally Controlled | Work Outcomes and Results of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Time Pressure | Frequency of Decision Making | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Clinical Nurse Specialists | Critical Care Nurses | Emergency Medical Technicians | Emergency Medicine Physicians | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Nurse Anesthetists | Nurse Practitioners | Occupational Therapy Aides | Occupational Therapy Assistants | Orderlies | Paramedics | Physical Therapist Aides | Psychiatric Aides | Psychiatric Technicians | Registered Nurses | Surgical Assistants</t>
+  </si>
+  <si>
+    <t>Provide or assist with basic care or support under the direction of onsite licensed nursing staff. Perform duties such as monitoring of health status, feeding, bathing, dressing, grooming, toileting, or ambulation of patients in a health or nursing facility. May include medication administration and other health-related tasks. Includes nursing care attendants, nursing aides, and nursing attendants.</t>
+  </si>
+  <si>
+    <t>Administer medications or treatments, such as catheterizations, suppositories, irrigations, enemas, massages, or douches, as directed by a physician or nurse. | Answer patient call signals, signal lights, bells, or intercom systems to determine patients' needs. | Apply clean dressings, slings, stockings, or support bandages, under direction of nurse or physician. | Assist nurses or physicians in the operation of medical equipment or provision of patient care. | Change bed linens or make beds. | Clean and sanitize patient rooms, bathrooms, examination rooms, or other patient areas. | Collect specimens, such as urine, feces, or sputum. | Communicate with patients to ascertain feelings or need for assistance or social and emotional support. | Document or otherwise report observations of patient behavior, complaints, or physical symptoms to nurses. | Exercise patients who are comatose, paralyzed, or have restricted mobility. | Explain medical instructions to patients or family members. | Feed patients or assist patients to eat or drink. | Gather information from caregivers, nurses, or physicians about patient condition, treatment plans, or appropriate activities. | Lift or assist others to lift patients to move them on or off beds, examination tables, surgical tables, or stretchers. | Measure and record food and liquid intake or urinary and fecal output, reporting changes to medical or nursing staff. | Observe or examine patients to detect symptoms that may require medical attention, such as bruises, open wounds, or blood in urine. | Position or hold patients in position for surgical preparation. | Prepare or serve food trays. | Provide information, such as directions, visiting hours, or patient status information to visitors or callers. | Provide physical support to assist patients to perform daily living activities, such as getting out of bed, bathing, dressing, using the toilet, standing, walking, or exercising. | Record height or weight of patients. | Record vital signs, such as temperature, blood pressure, pulse, or respiration rate, as directed by medical or nursing staff. | Remind patients to take medications or nutritional supplements. | Restock patient rooms with personal hygiene items, such as towels, washcloths, soap, or toilet paper. | Review patients' dietary restrictions, food allergies, and preferences to ensure patient receives appropriate diet. | Set up treating or testing equipment, such as oxygen tents, portable radiograph (x-ray) equipment, or overhead irrigation bottles, as directed by a physician or nurse. | Stock or issue medical supplies, such as dressing packs or treatment trays. | Supply, collect, or empty bedpans. | Transport patients to treatment units, testing units, operating rooms, or other areas, using wheelchairs, stretchers, or moveable beds. | Transport specimens, laboratory items, or pharmacy items, ensuring proper documentation and delivery to authorized personnel. | Turn or reposition bedridden patients. | Undress, wash, and dress patients who are unable to do so for themselves. | Wash, groom, shave, or drape patients to prepare them for surgery, treatment, or examination.</t>
+  </si>
+  <si>
+    <t>31-1132.00</t>
+  </si>
+  <si>
+    <t>Orderlies</t>
+  </si>
+  <si>
+    <t>Attendant | Operating Room Assistant | Orderly | Patient Care Assistant (PCA) | Patient Care Technician (PCT) | Patient Escort | Patient Transporter | Radiology Transporter | Transporter</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | GE Healthcare Centricity EMR | Medical record charting software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Trunk Strength | Speech Recognition | Problem Sensitivity | Static Strength | Oral Expression | Near Vision | Speech Clarity | Extent Flexibility | Dynamic Strength | Explosive Strength | Manual Dexterity | Gross Body Equilibrium | Stamina</t>
+  </si>
+  <si>
+    <t>Contact With Others | Physical Proximity | Exposed to Disease or Infections | Telephone Conversations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Walking or Running | Spend Time Standing | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Spend Time Bending or Twisting Your Body | Spend Time Making Repetitive Motions | Time Pressure | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Freedom to Make Decisions | Dealing With Unpleasant, Angry, or Discourteous People | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Determine Tasks, Priorities and Goals | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Anesthesiologist Assistants | Cardiovascular Technologists and Technicians | Emergency Medical Technicians | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Medical Equipment Preparers | Nursing Assistants | Occupational Therapy Assistants | Paramedics | Patient Representatives | Personal Care Aides | Physical Therapist Aides | Psychiatric Aides | Registered Nurses | Respiratory Therapists | Surgical Assistants | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Transport patients to areas such as operating rooms or x-ray rooms using wheelchairs, stretchers, or moveable beds. May maintain stocks of supplies or clean and transport equipment. Psychiatric orderlies are included in Psychiatric Aides.</t>
+  </si>
+  <si>
+    <t>Answer patient call signals, signal lights, bells, or intercom systems to determine patients' needs. | Carry messages or documents between departments. | Change soiled linens, such as bed linens, drapes, or cubicle curtains. | Clean and sanitize patient rooms, bathrooms, examination rooms, or other patient areas. | Clean equipment, such as wheelchairs, hospital beds, or portable medical equipment, documenting needed repairs or maintenance. | Collect and transport infectious or hazardous waste in closed containers for sterilization or disposal, in accordance with applicable law, standards, or policies. | Collect soiled linen or trash. | Disinfect or sterilize equipment or supplies, using germicides or sterilizing equipment. | Lift or assist others to lift patients to move them on or off beds, examination tables, surgical tables, or stretchers. | Position or hold patients in position for surgical preparation. | Provide physical support to patients to assist them to perform daily living activities, such as getting out of bed, bathing, dressing, using the toilet, standing, walking, or exercising. | Respond to emergency situations, such as emergency medical calls, security calls, or fire alarms. | Restrain patients to prevent violence or injury or to assist physicians or nurses to administer treatments. | Separate collected materials for disposal, recycling, or reuse, in accordance with environmental policies. | Serve or collect food trays. | Stock or issue medical supplies, such as dressing packs or treatment trays. | Stock utility rooms, nonmedical storage rooms, or cleaning carts with supplies. | Transport bodies to the morgue. | Transport patients to treatment units, testing units, operating rooms, or other areas, using wheelchairs, stretchers, or moveable beds. | Transport portable medical equipment or medical supplies between rooms or departments. | Transport specimens, laboratory items, or pharmacy items, ensuring proper documentation and delivery to authorized personnel. | Turn or reposition bedridden patients, alone or with assistance, to prevent bedsores.</t>
+  </si>
+  <si>
+    <t>31-1133.00</t>
+  </si>
+  <si>
+    <t>Psychiatric Aides</t>
+  </si>
+  <si>
+    <t>Developmental Aide | Mental Health Aide (MHA) | Mental Health Worker (MHW) | Psychiatric Aide | Psychiatric Assistant | Psychiatric Nursing Aide | Qualified Medication Aide (QMA) | Resident Care Technician (Resident Care Tech) | Residential Care Tech (Residential Care Technician) | Therapeutic Program Worker (TPW)</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Patient management software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Critical Thinking | Active Learning | Reading Comprehension | Writing</t>
+  </si>
+  <si>
+    <t>Psychology | Customer and Personal Service | Therapy and Counseling | English Language</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Problem Sensitivity | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Speech Recognition | Information Ordering | Far Vision | Near Vision | Written Expression | Selective Attention | Perceptual Speed | Flexibility of Closure | Category Flexibility | Auditory Attention | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Contact With Others | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Disease or Infections | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Health and Safety of Other Workers | Consequence of Error | Indoors, Environmentally Controlled | Telephone Conversations | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Importance of Being Exact or Accurate | Time Pressure | Dealing with Violent or Physically Aggressive People | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Clinical Nurse Specialists | Emergency Medicine Physicians | Healthcare Social Workers | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Nurse Practitioners | Nursing Assistants | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Therapist Aides | Physical Therapist Assistants | Psychiatric Technicians | Psychiatrists | Recreational Therapists | Registered Nurses</t>
+  </si>
+  <si>
+    <t>Assist mentally impaired or emotionally disturbed patients, working under direction of nursing and medical staff. May assist with daily living activities, lead patients in educational and recreational activities, or accompany patients to and from examinations and treatments. May restrain violent patients. Includes psychiatric orderlies.</t>
+  </si>
+  <si>
+    <t>Accompany patients to and from wards for medical or dental treatments, shopping trips, or religious or recreational events. | Aid patients in becoming accustomed to hospital routines. | Clean and disinfect rooms and furnishings to maintain a safe and orderly environment. | Complete administrative tasks, such as entering orders into computer, answering telephone calls, or maintaining medical or facility information. | Complete physical checks and monitor patients to detect unusual or harmful behavior and report observations to professional staff. | Interview patients upon admission and record information. | Listen and provide emotional support and encouragement to psychiatric patients. | Maintain patients' restrictions to assigned areas. | Organize, supervise, or encourage patient participation in social, educational, or recreational activities. | Participate in recreational activities with patients, including card games, sports, or television viewing. | Perform nursing duties, such as administering medications, measuring vital signs, collecting specimens, or drawing blood samples. | Provide patients with assistance in bathing, dressing, or grooming, demonstrating these skills as necessary. | Provide patients with cognitive, intellectual, or developmental disabilities with routine physical, emotional, psychological, or rehabilitation care under the direction of nursing or medical staff. | Record and maintain patient information, such as vital signs, eating habits, behavior, progress notes, treatments, or discharge plans. | Restrain or aid patients as necessary to prevent injury. | Serve meals or feed patients needing assistance or persuasion. | Work as part of a team that may include psychiatrists, psychologists, psychiatric nurses, or social workers.</t>
+  </si>
+  <si>
+    <t>31-2011.00</t>
+  </si>
+  <si>
+    <t>Occupational Therapy Assistants</t>
+  </si>
+  <si>
+    <t>Acute Care Occupational Therapy Assistant (Acute Care OT Assistant) | Certified Occupational Assistant | Certified Occupational Therapist Assistant (COTA) | Certified Occupational Therapy Assistant (COTA) | Licensed Occupational Therapist Assistant (LOTA) | Licensed Occupational Therapy Assistant (LOTA) | Occupational Therapist Assistant (OTA) | Occupational Therapy Assistant (OTA) | Registered Therapist Assistant | School Based Certified Occupational Therapy Assistant (School Based COTA)</t>
+  </si>
+  <si>
+    <t>Billing software | Bookkeeping software | BrainTrain Captain's Log | BrainTrain IVA+Plus | BrainTrain SmartDriver | Client caseload management software | Database software | Email software | Facebook | Fifth Walk BillingTracker | FileMaker Pro | Financial record software | Graphics software | Laboratory information system LIS | Language arts educational software | Math educational software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Patient documentation software | Scheduling software | Screen reader software | SpectraSoft DocuPRO | Text scanning software | TheraClin Systems iMAPR | Visual Health Information VHI PC-Kits | Web browser software | dBASE | eClinicalWorks EHR software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Monitoring | Critical Thinking | Writing | Learning Strategies | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Psychology | Education and Training | English Language | Therapy and Counseling | Public Safety and Security | Sociology and Anthropology | Administrative | Medicine and Dentistry | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Expression | Problem Sensitivity | Written Comprehension | Near Vision | Speech Clarity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Speech Recognition | Static Strength | Fluency of Ideas | Finger Dexterity | Category Flexibility | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Contact With Others | Physical Proximity | Time Pressure | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Health and Safety of Other Workers | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Standing | Spend Time Walking or Running | Importance of Repeating Same Tasks | Dealing With Unpleasant, Angry, or Discourteous People | Work Outcomes and Results of Other Workers | Spend Time Making Repetitive Motions | E-Mail</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Clinical Nurse Specialists | Emergency Medicine Physicians | Licensed Practical and Licensed Vocational Nurses | Massage Therapists | Medical Assistants | Nurse Practitioners | Occupational Therapists | Occupational Therapy Aides | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Psychiatric Aides | Psychiatric Technicians | Radiation Therapists | Recreational Therapists | Registered Nurses | Respiratory Therapists</t>
+  </si>
+  <si>
+    <t>Assist occupational therapists in providing occupational therapy treatments and procedures. May, in accordance with state laws, assist in development of treatment plans, carry out routine functions, direct activity programs, and document the progress of treatments. Generally requires formal training.</t>
+  </si>
+  <si>
+    <t>Aid patients in dressing and grooming themselves. | Alter treatment programs to obtain better results if treatment is not having the intended effect. | Assemble, clean, or maintain equipment or materials for patient use. | Assist educational specialists or clinical psychologists in administering situational or diagnostic tests to measure client's abilities or progress. | Attend care plan meetings to review patient progress and update care plans. | Attend continuing education classes. | Communicate and collaborate with other healthcare professionals involved with the care of a patient. | Demonstrate therapy techniques, such as manual or creative arts or games. | Design, fabricate, or repair assistive devices or make adaptive changes to equipment or environments. | Evaluate the daily living skills or capacities of clients with physical, developmental, or mental health disabilities. | Implement, or assist occupational therapists with implementing, treatment plans designed to help clients function independently. | Instruct, or assist in instructing, patients and families in home programs, basic living skills, or the care and use of adaptive equipment. | Maintain and promote a positive attitude toward clients and their treatment programs. | Monitor patients' performance in therapy activities, providing encouragement. | Observe and record patients' progress, attitudes, and behavior and maintain this information in client records. | Order any needed educational or treatment supplies. | Perform clerical duties, such as scheduling appointments, collecting data, or documenting health insurance billings. | Report to supervisors, verbally or in writing, on patients' progress, attitudes, and behavior. | Select therapy activities to fit patients' needs and capabilities. | Teach patients how to deal constructively with their emotions. | Transport patients to and from the occupational therapy work area. | Work under the direction of occupational therapists to plan, implement, or administer educational, vocational, or recreational programs that restore or enhance performance in individuals with functional impairments.</t>
+  </si>
+  <si>
+    <t>31-2012.00</t>
+  </si>
+  <si>
+    <t>Occupational Therapy Aides</t>
+  </si>
+  <si>
+    <t>Certified Occupational Rehabilitation Aide (CORA) | Direct Service Professional (DSP) | Direct Support Professional (DSP) | Occupational Rehabilitation Aide | Occupational Therapist Aide (OT Aide) | Occupational Therapy Aide (OT Aide) | Rehabilitation Aide (Rehab Aide) | Rehabilitation Services Aide | Restorative Aide</t>
+  </si>
+  <si>
+    <t>Billing software | Electronic medical record EMR software | MEDITECH software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Scheduling software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Monitoring | Reading Comprehension | Writing | Learning Strategies | Active Learning</t>
+  </si>
+  <si>
+    <t>Therapy and Counseling | English Language | Customer and Personal Service | Psychology | Computers and Electronics | Education and Training | Medicine and Dentistry | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Deductive Reasoning | Speech Recognition | Speech Clarity | Information Ordering | Written Expression | Written Comprehension | Near Vision | Trunk Strength | Finger Dexterity | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Physical Proximity | Health and Safety of Other Workers | Exposed to Disease or Infections | Time Pressure | Impact of Decisions on Co-workers or Company Results | Dealing With Unpleasant, Angry, or Discourteous People | Frequency of Decision Making | Telephone Conversations | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Spend Time Standing | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Clinical Nurse Specialists | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Mental Health and Substance Abuse Social Workers | Nursing Assistants | Occupational Therapists | Occupational Therapy Assistants | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Psychiatric Aides | Psychiatric Technicians | Recreational Therapists | Registered Nurses | Rehabilitation Counselors | Respiratory Therapists</t>
+  </si>
+  <si>
+    <t>Under close supervision of an occupational therapist or occupational therapy assistant, perform only delegated, selected, or routine tasks in specific situations. These duties include preparing patient and treatment room.</t>
+  </si>
+  <si>
+    <t>Accompany patients on outings, providing transportation when necessary. | Adjust and repair assistive devices and make adaptive changes to other equipment and to environments. | Assist educational specialists or clinical psychologists in administering situational or diagnostic tests to measure client's abilities or progress. | Assist occupational therapists in planning, implementing, and administering therapy programs to restore, reinforce, and enhance performance, using selected activities and special equipment. | Demonstrate therapy techniques, such as manual and creative arts and games. | Encourage patients and attend to their physical needs to facilitate the attainment of therapeutic goals. | Evaluate the living skills and capacities of clients with physical, developmental, or mental health disabilities. | Instruct patients and families in work, social, and living skills, the care and use of adaptive equipment, and other skills to facilitate home and work adjustment to disability. | Manage intradepartmental infection control and equipment security. | Observe patients' attendance, progress, attitudes, and accomplishments and record and maintain information in client records. | Perform clerical, administrative, and secretarial duties, such as answering phones, restocking and ordering supplies, filling out paperwork, and scheduling appointments. | Prepare and maintain work area, materials, and equipment and maintain inventory of treatment and educational supplies. | Report to supervisors or therapists, verbally or in writing, on patients' progress, attitudes, attendance, and accomplishments. | Supervise patients in choosing and completing work assignments or arts and crafts projects. | Transport patients to and from the occupational therapy work area.</t>
+  </si>
+  <si>
+    <t>31-2021.00</t>
+  </si>
+  <si>
+    <t>Physical Therapist Assistants</t>
+  </si>
+  <si>
+    <t>Certified Physical Therapist Assistant (CPTA) | Home Care Physical Therapy Assistant | Home Health Physical Therapist Assistant | Licensed Physical Therapist Assistant (LPTA) | Licensed Physical Therapy Assistant | Outpatient Physical Therapist Assistant | Per Diem Physical Therapist Assistant (Per Diem PTA) | Physical Therapist Assistant (PTA) | Physical Therapy Assistant (PTA)</t>
+  </si>
+  <si>
+    <t>Arena Health Systems Phys-X | Beaver Creek Software The THERAPIST | Billing software | BioEx Systems Exercise Pro | Bookkeeping software | Client caseload management software | Eazy Application Systems QuickEMR | Email software | FileMaker Pro | Knees Software PT DocTools | Laboratory information system LIS | Medical condition coding software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | PhysioTools Tools RG | Rehab Documentation Company ReDoc Suite | Scheduling software | SpectraSoft AppointmentsPRO | SpectraSoft DocuPRO | Summit Software CarePoint | TherAssist | Video game software | Virtual reality game software | dBASE | eClinicalWorks EHR software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Active Learning | Critical Thinking | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Therapy and Counseling | English Language | Education and Training | Psychology | Medicine and Dentistry | Computers and Electronics | Biology</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Written Comprehension | Problem Sensitivity | Near Vision | Written Expression | Deductive Reasoning | Selective Attention | Inductive Reasoning | Static Strength | Arm-Hand Steadiness | Information Ordering | Fluency of Ideas | Far Vision | Trunk Strength | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Visualization | Perceptual Speed | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Physical Proximity | Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Exposed to Disease or Infections | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Deal With External Customers or the Public in General | Freedom to Make Decisions | Consequence of Error | Spend Time Standing | Spend Time Making Repetitive Motions | Spend Time Bending or Twisting Your Body | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Emergency Medicine Physicians | Licensed Practical and Licensed Vocational Nurses | Massage Therapists | Medical Assistants | Nurse Practitioners | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapists | Physician Assistants | Psychiatric Aides | Psychiatric Technicians | Radiation Therapists | Recreational Therapists | Respiratory Therapists | Surgical Assistants</t>
+  </si>
+  <si>
+    <t>Assist physical therapists in providing physical therapy treatments and procedures. May, in accordance with state laws, assist in the development of treatment plans, carry out routine functions, document the progress of treatment, and modify specific treatments in accordance with patient status and within the scope of treatment plans established by a physical therapist. Generally requires formal training.</t>
+  </si>
+  <si>
+    <t>Administer active or passive manual therapeutic exercises, therapeutic massage, aquatic physical therapy, or heat, light, sound, or electrical modality treatments, such as ultrasound. | Administer traction to relieve neck or back pain, using intermittent or static traction equipment. | Assist patients to dress, undress, or put on and remove supportive devices, such as braces, splints, or slings. | Attend or conduct continuing education courses, seminars, or in-service activities. | Clean work area and check and store equipment after treatment. | Communicate with or instruct caregivers or family members on patient therapeutic activities or treatment plans. | Confer with physical therapy staff or others to discuss and evaluate patient information for planning, modifying, or coordinating treatment. | Document patient information, such as notes on their progress. | Fit patients for orthopedic braces, prostheses, or supportive devices, such as crutches. | Instruct patients in proper body mechanics and in ways to improve functional mobility, such as aquatic exercise. | Instruct, motivate, safeguard, and assist patients as they practice exercises or functional activities. | Measure patients' range-of-joint motion, body parts, or vital signs to determine effects of treatments or for patient evaluations. | Monitor operation of equipment and record use of equipment and administration of treatment. | Observe patients during treatments to compile and evaluate data on their responses and progress and provide results to physical therapist in person or through progress notes. | Perform clerical duties, such as taking inventory, ordering supplies, answering telephone, taking messages, or filling out forms. | Perform postural drainage, percussions, or vibrations or teach deep breathing exercises to treat respiratory conditions. | Perform therapeutic wound care. | Prepare treatment areas and electrotherapy equipment for use by physiotherapists. | Secure patients into or onto therapy equipment. | Train patients in the use of orthopedic braces, prostheses, or supportive devices. | Transport patients to and from treatment areas, lifting and transferring them according to positioning requirements.</t>
+  </si>
+  <si>
+    <t>31-2022.00</t>
+  </si>
+  <si>
+    <t>Physical Therapist Aides</t>
+  </si>
+  <si>
+    <t>PT Attendant (Physical Therapy Attendant) | PT Tech (Physical Therapist Technician) | PT Tech (Physical Therapy Technician) | Physical Therapist Aide (PTA) | Physical Therapy Aide (PTA) | Rehabilitation Aide | Rehabilitation Attendant | Rehabilitation Technician (Rehabilitation Tech) | Restorative Aide (RA) | Therapy Aide</t>
+  </si>
+  <si>
+    <t>Epic Systems | MEDITECH software | Medical procedure coding software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Patient record maintenance software | Scheduling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Reading Comprehension | Active Learning | Critical Thinking | Speaking | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Computers and Electronics | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Speech Recognition | Near Vision | Oral Expression | Written Comprehension | Speech Clarity | Trunk Strength | Selective Attention | Information Ordering | Inductive Reasoning | Written Expression</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Health and Safety of Other Workers | Indoors, Environmentally Controlled | Spend Time Standing | Telephone Conversations | Spend Time Walking or Running | Freedom to Make Decisions | Exposed to Disease or Infections | E-Mail | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Emergency Medicine Physicians | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Massage Therapists | Medical Assistants | Nursing Assistants | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Orthopedic Surgeons, Except Pediatric | Physical Medicine and Rehabilitation Physicians | Physical Therapist Assistants | Physical Therapists | Psychiatric Aides | Psychiatric Technicians | Radiation Therapists | Recreational Therapists | Respiratory Therapists</t>
+  </si>
+  <si>
+    <t>Under close supervision of a physical therapist or physical therapy assistant, perform only delegated, selected, or routine tasks in specific situations. These duties include preparing the patient and the treatment area.</t>
+  </si>
+  <si>
+    <t>Administer active or passive manual therapeutic exercises, therapeutic massage, or heat, light, sound, water, or electrical modality treatments, such as ultrasound. | Administer traction to relieve neck or back pain, using intermittent or static traction equipment. | Arrange treatment supplies to keep them in order. | Assist patients to dress, undress, or put on and remove supportive devices, such as braces, splints, or slings. | Change linens, such as bed sheets and pillow cases. | Clean and organize work area and disinfect equipment after treatment. | Confer with physical therapy staff or others to discuss and evaluate patient information for planning, modifying, or coordinating treatment. | Fit patients for orthopedic braces, prostheses, or supportive devices, adjusting fit as needed. | Instruct, motivate, safeguard, or assist patients practicing exercises or functional activities, under direction of medical staff. | Maintain equipment or furniture to keep it in good working condition, including performing the assembly or disassembly of equipment or accessories. | Measure patient's range-of-joint motion, body parts, or vital signs to determine effects of treatments or for patient evaluations. | Observe patients during treatment to compile and evaluate data on patients' responses and progress and report to physical therapist. | Participate in patient care tasks, such as assisting with passing food trays, feeding residents, or bathing residents on bed rest. | Perform clerical duties, such as taking inventory, ordering supplies, answering telephone, taking messages, or filling out forms. | Record treatment given and equipment used. | Schedule patient appointments with physical therapists and coordinate therapists' schedules. | Secure patients into or onto therapy equipment. | Train patients to use orthopedic braces, prostheses, or supportive devices. | Transport patients to and from treatment areas, using wheelchairs or providing standing support.</t>
+  </si>
+  <si>
+    <t>31-9011.00</t>
+  </si>
+  <si>
+    <t>Massage Therapists</t>
+  </si>
+  <si>
+    <t>Bodywork Therapist | Certified Massage Therapist (CMT) | Clinical Massage Therapist | Integrated Deep Tissue Massage Therapist | Licensed Massage Practitioner (LMP) | Licensed Massage Therapist (LMT) | Massage Therapist | Registered Massage Therapist (RMT) | Soft Tissue Specialist | Therapeutic Massage Technician</t>
+  </si>
+  <si>
+    <t>AppointmentQuest Online Appointment Manager | ICS Software SammyUSA | Land Software Customer Pro-File | Massage Suite | Microsoft Excel | Microsoft Word | Scheduling software | WinCity Custom Software WinCity Massage SOAP Notes</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Biology | English Language | Psychology | Medicine and Dentistry | Public Safety and Security | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Dynamic Strength | Trunk Strength | Oral Comprehension | Oral Expression | Manual Dexterity | Multilimb Coordination | Problem Sensitivity | Extent Flexibility | Stamina | Finger Dexterity | Arm-Hand Steadiness | Selective Attention | Speech Clarity | Deductive Reasoning | Written Expression | Written Comprehension | Inductive Reasoning | Speech Recognition | Near Vision | Static Strength</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Contact With Others | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Frequency of Decision Making | Physical Proximity | Spend Time Standing | Telephone Conversations | Deal With External Customers or the Public in General | Spend Time Bending or Twisting Your Body | Impact of Decisions on Co-workers or Company Results | E-Mail | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Acupuncturists | Chiropractors | Dermatologists | Licensed Practical and Licensed Vocational Nurses | Naturopathic Physicians | Nurse Practitioners | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Radiation Therapists | Recreational Therapists | Registered Nurses | Respiratory Therapists | Skincare Specialists</t>
+  </si>
+  <si>
+    <t>Perform therapeutic massages of soft tissues and joints. May assist in the assessment of range of motion and muscle strength, or propose client therapy plans.</t>
+  </si>
+  <si>
+    <t>Apply finger and hand pressure to specific points of the body. | Assess clients' soft tissue condition, joint quality and function, muscle strength, and range of motion. | Confer with clients about their medical histories and problems with stress or pain to determine how massage will be most helpful. | Consult with other health care professionals, such as physiotherapists, chiropractors, physicians, and psychologists, to develop treatment plans for clients. | Develop and propose client treatment plans that specify which types of massage are to be used. | Maintain massage areas by restocking supplies or sanitizing equipment. | Maintain treatment records. | Massage and knead muscles and soft tissues of the body to provide treatment for medical conditions, injuries, or wellness maintenance. | Perform other adjunctive therapies or treatment techniques in addition to massage. | Prepare and blend oils and apply the blends to clients' skin. | Provide clients with guidance and information about techniques for postural improvement and stretching, strengthening, relaxation, and rehabilitative exercises. | Refer clients to other types of therapists when necessary. | Treat clients in professional settings or travel to clients' offices and homes. | Use complementary aids, such as infrared lamps, wet compresses, ice, and whirlpool baths to promote clients' recovery, relaxation, and well-being.</t>
+  </si>
+  <si>
+    <t>31-9091.00</t>
+  </si>
+  <si>
+    <t>Dental Assistants</t>
+  </si>
+  <si>
+    <t>Certified Dental Assistant (CDA) | Certified Registered Dental Assistant | Dental Assistant (DA) | Expanded Dental Assistant | Expanded Duty Dental Assistant (EDDA) | Expanded Functions Dental Assistant (EFDA) | Oral Surgery Assistant | Orthodontic Assistant (Ortho Assistant) | Registered Dental Assistant (RDA) | Surgical Dental Assistant</t>
+  </si>
+  <si>
+    <t>Email software | Henry Schein Dentrix | Kodak Dental Systems Kodak SOFTDENT Practice management software PMS | Microsoft Excel | Microsoft Office software | Open Dental | Patterson Dental Supply Patterson EagleSoft | Quicken | The Systems Workplace TDOCS | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Active Learning | Monitoring | Critical Thinking | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Medicine and Dentistry | English Language | Administration and Management | Administrative | Computers and Electronics | Sales and Marketing | Production and Processing</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Expression | Oral Comprehension | Speech Recognition | Written Comprehension | Deductive Reasoning | Information Ordering | Speech Clarity | Finger Dexterity | Arm-Hand Steadiness | Problem Sensitivity | Written Expression | Inductive Reasoning | Control Precision | Manual Dexterity | Time Sharing | Selective Attention | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Physical Proximity | Work With or Contribute to a Work Group or Team | Telephone Conversations | Health and Safety of Other Workers | Exposed to Radiation | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | E-Mail | Spend Time Making Repetitive Motions | Deal With External Customers or the Public in General | Spend Time Bending or Twisting Your Body | Frequency of Decision Making | Spend Time Standing | Exposed to Disease or Infections | Spend Time Walking or Running | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Cardiologists | Chiropractors | Dental Hygienists | Dental Laboratory Technicians | Dentists, General | Dermatologists | Endoscopy Technicians | Medical Assistants | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Ophthalmologists, Except Pediatric | Oral and Maxillofacial Surgeons | Orthodontists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Therapist Aides | Prosthodontists | Surgical Assistants | Surgical Technologists | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Perform limited clinical duties under the direction of a dentist. Clinical duties may include equipment preparation and sterilization, preparing patients for treatment, assisting the dentist during treatment, and providing patients with instructions for oral healthcare procedures. May perform administrative duties such as scheduling appointments, maintaining medical records, billing, and coding information for insurance purposes.</t>
+  </si>
+  <si>
+    <t>Apply protective coating of fluoride to teeth. | Assist dentist in management of medical or dental emergencies. | Clean and polish removable appliances. | Clean teeth, using dental instruments. | Expose dental diagnostic x-rays. | Fabricate and fit orthodontic appliances and materials for patients, such as retainers, wires, or bands. | Fabricate temporary restorations or custom impressions from preliminary impressions. | Instruct patients in oral hygiene and plaque control programs. | Make preliminary impressions for study casts and occlusal registrations for mounting study casts. | Order and monitor dental supplies and equipment inventory. | Pour, trim, and polish study casts. | Prepare patient, sterilize or disinfect instruments, set up instrument trays, prepare materials, or assist dentist during dental procedures. | Provide postoperative instructions prescribed by dentist. | Record treatment information in patient records. | Schedule appointments, prepare bills and receive payment for dental services, complete insurance forms, and maintain records, manually or using computer. | Take and record medical and dental histories and vital signs of patients.</t>
+  </si>
+  <si>
+    <t>31-9092.00</t>
+  </si>
+  <si>
+    <t>Medical Assistants</t>
+  </si>
+  <si>
+    <t>Certified Medical Assistant (CMA) | Chiropractor Assistant | Clinical Medical Assistant | Doctor's Assistant | Health Assistant | Ophthalmic Assistant | Ophthalmological Assistant | Optometric Assistant | Outpatient Surgery Assistant | Registered Medical Assistant (RMA)</t>
+  </si>
+  <si>
+    <t>Appointment scheduling software | Billing software | Bookkeeping software | Business software applications | Data entry software | Database software | Diagnostic and procedural coding software | Electronic medical record EMR software | Email software | Epic Systems | GE Healthcare Centricity EMR | Healthcare common procedure coding system HCPCS | IDX Systems Patient Chart Tracking | Intuit QuickBooks | MEDITECH software | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Windows Vista Business | Microsoft Windows XP Professional | Microsoft Word | Patient management software | Visual electro diagnostic software | Web browser software | eClinicalWorks EHR software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Medicine and Dentistry | Administrative | Computers and Electronics | Education and Training | Public Safety and Security | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Problem Sensitivity | Near Vision | Speech Recognition | Written Expression | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Information Ordering | Flexibility of Closure | Category Flexibility | Finger Dexterity | Arm-Hand Steadiness | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Contact With Others | Exposed to Disease or Infections | Indoors, Environmentally Controlled | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Telephone Conversations | Physical Proximity | Face-to-Face Discussions with Individuals and Within Teams | Written Letters and Memos | Importance of Repeating Same Tasks | Consequence of Error | Deal With External Customers or the Public in General | Dealing With Unpleasant, Angry, or Discourteous People | Frequency of Decision Making | Time Pressure | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Cardiologists | Cardiovascular Technologists and Technicians | Dental Assistants | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Licensed Practical and Licensed Vocational Nurses | Medical Records Specialists | Nurse Practitioners | Nursing Assistants | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Physical Therapist Aides | Physician Assistants | Registered Nurses | Surgical Assistants</t>
+  </si>
+  <si>
+    <t>Perform administrative and certain clinical duties under the direction of a physician. Administrative duties may include scheduling appointments, maintaining medical records, billing, and coding information for insurance purposes. Clinical duties may include taking and recording vital signs and medical histories, preparing patients for examination, drawing blood, and administering medications as directed by physician.</t>
+  </si>
+  <si>
+    <t>Authorize drug refills and provide prescription information to pharmacies. | Change dressings on wounds. | Clean and sterilize instruments and dispose of contaminated supplies. | Collect blood, tissue, or other laboratory specimens, log the specimens, and prepare them for testing. | Contact medical facilities or departments to schedule patients for tests or admission. | Explain treatment procedures, medications, diets, or physicians' instructions to patients. | Greet and log in patients arriving at office or clinic. | Help physicians examine and treat patients, handing them instruments or materials or performing such tasks as giving injections or removing sutures. | Interview patients to obtain medical information and measure their vital signs, weight, and height. | Inventory and order medical, lab, or office supplies or equipment. | Keep financial records or perform other bookkeeping duties, such as handling credit or collections or mailing monthly statements to patients. | Operate x-ray, electrocardiogram (EKG), or other equipment to administer routine diagnostic tests. | Perform general office duties, such as answering telephones, taking dictation, or completing insurance forms. | Perform routine laboratory tests and sample analyses. | Prepare and administer medications as directed by a physician. | Prepare treatment rooms for patient examinations, keeping the rooms neat and clean. | Record patients' medical history, vital statistics, or information such as test results in medical records. | Schedule appointments for patients. | Set up medical laboratory equipment. | Show patients to examination rooms and prepare them for the physician.</t>
+  </si>
+  <si>
+    <t>31-9093.00</t>
+  </si>
+  <si>
+    <t>Medical Equipment Preparers</t>
+  </si>
+  <si>
+    <t>Central Processing Technician (CPT) | Central Service Technician (CST) | Central Sterile Supply Technician (CSS Technician) | Certified Registered Central Service Technician (CRCST) | Instrument Technician | Sterile Preparation Technician | Sterile Processing Technician (Sterile Processing Tech) | Sterile Processing and Distribution Technician (SPD Tech) | Sterile Technician | Sterilization Technician</t>
+  </si>
+  <si>
+    <t>Calendar software | Database software | Email software | Inventory tracking software | Kronos Workforce Timekeeper | MEDITECH Supply Chain Management | MEDITECH software | McKesson ANSOS One-Staff | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Word | Pyxis MedStation software | eClinicalWorks EHR software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Reading Comprehension | Speaking | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Biology | Production and Processing | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Oral Comprehension | Manual Dexterity | Finger Dexterity | Oral Expression | Written Expression | Deductive Reasoning | Information Ordering | Perceptual Speed | Arm-Hand Steadiness | Speech Recognition | Trunk Strength | Category Flexibility | Written Comprehension | Control Precision | Visualization | Flexibility of Closure | Inductive Reasoning | Static Strength | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Telephone Conversations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Exposed to Disease or Infections | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Time Pressure | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | E-Mail | Frequency of Decision Making | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Spend Time Walking or Running | Work Outcomes and Results of Other Workers | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Consequence of Error | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Hazardous Conditions | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Anesthesiologist Assistants | Calibration Technologists and Technicians | Cardiovascular Technologists and Technicians | Chemical Plant and System Operators | Cytotechnologists | Emergency Medical Technicians | Endoscopy Technicians | Histotechnologists | Medical Equipment Repairers | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Phlebotomists | Radiologic Technologists and Technicians | Surgical Assistants | Surgical Technologists | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Prepare, sterilize, install, or clean laboratory or healthcare equipment. May perform routine laboratory tasks and operate or inspect equipment.</t>
+  </si>
+  <si>
+    <t>Assist hospital staff with patient care duties, such as providing transportation or setting up traction. | Attend hospital in-service programs related to areas of work specialization. | Check sterile supplies to ensure that they are not outdated. | Clean instruments to prepare them for sterilization. | Deliver equipment to specified hospital locations or to patients' residences. | Disinfect and sterilize equipment, such as respirators, hospital beds, or oxygen or dialysis equipment, using sterilizers, aerators, or washers. | Examine equipment to detect leaks, worn or loose parts, or other indications of disrepair. | Maintain records of inventory or equipment usage and order medical instruments or supplies when inventory is low. | Operate and maintain steam autoclaves, keeping records of loads completed, items in loads, and maintenance procedures performed. | Organize and assemble routine or specialty surgical instrument trays or other sterilized supplies, filling special requests as needed. | Purge wastes from equipment by connecting equipment to water sources and flushing water through systems. | Record sterilizer test results. | Report defective equipment to appropriate supervisors or staff. | Start equipment and observe gauges and equipment operation to detect malfunctions and to ensure equipment is operating to prescribed standards. | Stock crash carts or other medical supplies.</t>
+  </si>
+  <si>
+    <t>31-9094.00</t>
+  </si>
+  <si>
+    <t>Medical Transcriptionists</t>
+  </si>
+  <si>
+    <t>Clinical Medical Transcriptionist | Documentation Specialist | Medical Language Specialist | Medical Scribe | Medical Transcriber | Medical Transcriptionist | Pathology Transcriptionist | Radiology Transcriptionist | Scribe | Transcriptionist</t>
+  </si>
+  <si>
+    <t>Allscripts healthcare automation software | Boston Bar Systems Corporation Sonnet | Bytescribe Development Company WavPlayer | Calendar software | Corel WordPerfect Office Suite | Crescendo Systems Corporation MedRite-XL | Crescendo Systems DigiScribe-XL | Database software | Electronic medical record EMR systems | Email software | Emmaus MPWord | FileMaker Pro | Healthcare common procedure coding system HCPCS | Integrated Systems Management OmniMD | MedQuist DocQment Enterprise Platform | Medical terminology databases | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Narratek Smartype | Nuance Dragon NaturallySpeaking | PCC EHR | Patient billing software | Precision Data Solutions VoicePower | Prognosis Innovation Healthcare ChartAccess | SpectraMedi EasyFlow | Speech recognition software | SpeedType | SpeedUp Trans | Spellex AccuCount | Sylvan Software Complete Medical Pharmaceutical Spell Checker | Sylvan Software DropChute Pro | Sylvan Software ShortCut | Web browser software | YouTube | dBASE Plus | eClinicalWorks EHR software | g-net solutions MTP</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Writing | Monitoring | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>English Language | Administrative | Computers and Electronics | Medicine and Dentistry</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Speech Recognition | Written Expression | Near Vision | Oral Expression | Information Ordering | Category Flexibility | Selective Attention | Speech Clarity | Finger Dexterity | Perceptual Speed | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Importance of Repeating Same Tasks | E-Mail | Contact With Others | Telephone Conversations | Determine Tasks, Priorities and Goals | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Health and Safety of Other Workers | Frequency of Decision Making | Freedom to Make Decisions | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Sitting | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Cardiologists | Cardiovascular Technologists and Technicians | Court Reporters and Simultaneous Captioners | Diagnostic Medical Sonographers | Emergency Medical Technicians | Emergency Medicine Physicians | File Clerks | Health Information Technologists and Medical Registrars | Medical Assistants | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Neurodiagnostic Technologists | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Pharmacy Technicians | Phlebotomists | Radiologic Technologists and Technicians | Receptionists and Information Clerks | Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>Transcribe medical reports recorded by physicians and other healthcare practitioners using various electronic devices, covering office visits, emergency room visits, diagnostic imaging studies, operations, chart reviews, and final summaries. Transcribe dictated reports and translate abbreviations into fully understandable form. Edit as necessary and return reports in either printed or electronic form for review and signature, or correction.</t>
+  </si>
+  <si>
+    <t>Answer inquiries concerning the progress of medical cases, within the limits of confidentiality laws. | Decide which information should be included or excluded in reports. | Distinguish between homonyms and recognize inconsistencies and mistakes in medical terms, referring to dictionaries, drug references, and other sources on anatomy, physiology, and medicine. | Identify mistakes in reports and check with doctors to obtain the correct information. | Perform a variety of clerical and office tasks, such as handling incoming and outgoing mail, completing and submitting insurance claims, typing, filing, or operating office machines. | Perform data entry and data retrieval services, providing data for inclusion in medical records and for transmission to physicians. | Produce medical reports, correspondence, records, patient-care information, statistics, medical research, and administrative material. | Receive and screen telephone calls and visitors. | Receive patients, schedule appointments, and maintain patient records. | Return dictated reports in printed or electronic form for physician's review, signature, and corrections and for inclusion in patients' medical records. | Review and edit transcribed reports or dictated material for spelling, grammar, clarity, consistency, and proper medical terminology. | Set up and maintain medical files and databases, including records such as x-ray, lab, and procedure reports, medical histories, diagnostic workups, admission and discharge summaries, and clinical resumes. | Take dictation using shorthand, a stenotype machine, or headsets and transcribing machines. | Transcribe dictation for a variety of medical reports, such as patient histories, physical examinations, emergency room visits, operations, chart reviews, consultation, or discharge summaries. | Translate medical jargon and abbreviations into their expanded forms to ensure the accuracy of patient and health care facility records.</t>
+  </si>
+  <si>
+    <t>31-9095.00</t>
+  </si>
+  <si>
+    <t>Pharmacy Aides</t>
+  </si>
+  <si>
+    <t>Certified Pharmacist Assistant | Drug Purchaser | Front Counter Clerk | Pharmacist Assistant | Pharmacy Aide | Pharmacy Ancillary | Pharmacy Assistant | Pharmacy Cashier | Pharmacy Clerk</t>
+  </si>
+  <si>
+    <t>Database software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Speech Clarity | Oral Expression | Speech Recognition | Near Vision | Written Comprehension | Problem Sensitivity | Information Ordering | Finger Dexterity | Category Flexibility | Deductive Reasoning | Written Expression</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Telephone Conversations | Spend Time Standing | Contact With Others | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Exposed to Disease or Infections | Determine Tasks, Priorities and Goals | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | E-Mail | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Cashiers | Counter and Rental Clerks | Customer Service Representatives | First-Line Supervisors of Retail Sales Workers | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Medical Equipment Preparers | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Nursing Assistants | Office Clerks, General | Opticians, Dispensing | Pharmacists | Pharmacy Technicians | Phlebotomists | Receptionists and Information Clerks | Retail Salespersons | Stockers and Order Fillers | Veterinary Assistants and Laboratory Animal Caretakers | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Record drugs delivered to the pharmacy, store incoming merchandise, and inform the supervisor of stock needs. May operate cash register and accept prescriptions for filling.</t>
+  </si>
+  <si>
+    <t>Accept prescriptions for filling, gathering and processing necessary information. | Answer telephone inquiries, referring callers to pharmacist when necessary. | Compound, package, and label pharmaceutical products, under direction of pharmacist. | Deliver medication to treatment areas, living units, residences, or clinics, using various means of transportation. | Greet customers and help them locate merchandise. | Maintain and clean equipment, work areas, or shelves. | Operate cash register to process cash or credit sales. | Perform clerical tasks, such as filing, compiling and maintaining prescription records, or composing letters. | Prepare prescription labels by typing or operating a computer and printer. | Prepare, maintain, and record records of inventories, receipts, purchases, or deliveries, using a variety of computer screen formats. | Process medical insurance claims, posting bill amounts and calculating copayments. | Receive, store, and inventory pharmaceutical supplies or medications, check for out-of-date medications, and notify pharmacist when inventory levels are low. | Restock storage areas, replenishing items on shelves. | Unpack, sort, count, and label incoming merchandise, including items requiring special handling or refrigeration.</t>
+  </si>
+  <si>
+    <t>31-9096.00</t>
+  </si>
+  <si>
+    <t>Veterinary Assistants and Laboratory Animal Caretakers</t>
+  </si>
+  <si>
+    <t>Animal Care Provider | Animal Caregiver | Avian Keeper | Certified Veterinary Assistant | Emergency Veterinary Assistant | Inpatient Technician Assistant | Kennel Vet Assistant (Kennel Veterinary Assistant) | Research Animal Attendant | Small Animal Caretaker | Veterinarian Assistant (Vet Assistant)</t>
+  </si>
+  <si>
+    <t>IDEXX Laboratories IDEXX Cornerstone | Labeling software | McAllister Software Systems AVImark | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Practice management software PMS | Scheduling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Reading Comprehension | Writing | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Biology | Administrative | Medicine and Dentistry | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Written Expression | Problem Sensitivity | Information Ordering | Manual Dexterity | Deductive Reasoning | Near Vision | Written Comprehension | Speech Clarity | Speech Recognition | Extent Flexibility | Trunk Strength | Multilimb Coordination | Finger Dexterity | Arm-Hand Steadiness | Selective Attention | Flexibility of Closure | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Spend Time Standing | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Exposed to Disease or Infections | Telephone Conversations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Physical Proximity | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Frequency of Decision Making | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Walking or Running | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Exposed to Radiation | Consequence of Error | Deal With External Customers or the Public in General | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | E-Mail | Exposed to Cramped Work Space, Awkward Positions | Spend Time Kneeling, Crouching, Stooping, or Crawling | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Allergists and Immunologists | Animal Caretakers | Cardiovascular Technologists and Technicians | Emergency Medical Technicians | Emergency Medicine Physicians | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Medical and Clinical Laboratory Technologists | Nurse Practitioners | Nursing Assistants | Paramedics | Pharmacists | Phlebotomists | Physician Assistants | Physicians, Pathologists | Registered Nurses | Surgical Assistants | Veterinarians | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Feed, water, and examine pets and other nonfarm animals for signs of illness, disease, or injury in laboratories and animal hospitals and clinics. Clean and disinfect cages and work areas, and sterilize laboratory and surgical equipment. May provide routine postoperative care, administer medication orally or topically, or prepare samples for laboratory examination under the supervision of veterinary or laboratory animal technologists or technicians, veterinarians, or scientists.</t>
+  </si>
+  <si>
+    <t>Administer anesthetics during surgery and monitor the effects on animals. | Administer medication, immunizations, or blood plasma to animals as prescribed by veterinarians. | Assist veterinarians in examining animals to determine the nature of illnesses or injuries. | Clean and maintain kennels, animal holding areas, examination or operating rooms, or animal loading or unloading facilities to control the spread of disease. | Clean, maintain, and sterilize instruments or equipment. | Collect laboratory specimens, such as blood, urine, or feces, for testing. | Dust, spray, or bathe animals to control insect pests. | Educate or advise clients on animal health care, nutrition, or behavior problems. | Examine animals to detect behavioral changes or clinical symptoms that could indicate illness or injury. | Exercise animals or provide them with companionship. | Fill medication prescriptions. | Groom, trim, or clip animals' coats. | Hold or restrain animals during veterinary procedures. | Monitor animals recovering from surgery and notify veterinarians of any unusual changes or symptoms. | Perform accounting duties, such as bookkeeping, billing customers for services, or maintaining inventories. | Perform enemas, catheterizations, ear flushes, intravenous feedings, or gavages. | Perform hygiene-related duties, such as clipping animals' claws or cleaning and polishing teeth. | Perform office reception duties, such as scheduling appointments or helping customers. | Perform routine laboratory tests or diagnostic tests, such as taking or developing x-rays. | Place orders to restock inventory of hospital or laboratory supplies. | Prepare examination or treatment rooms by stocking them with appropriate supplies. | Prepare feed for animals according to specific instructions, such as diet lists or schedules. | Prepare surgical equipment and pass instruments or materials to veterinarians during surgical procedures. | Provide assistance with euthanasia of animals or disposal of corpses. | Provide emergency first aid to sick or injured animals. | Record information relating to animal genealogy, feeding schedules, appearance, behavior, or breeding. | Sell pet food or supplies to customers. | Write reports, maintain research information, or perform clerical duties.</t>
+  </si>
+  <si>
+    <t>31-9097.00</t>
+  </si>
+  <si>
+    <t>Phlebotomists</t>
+  </si>
+  <si>
+    <t>Lab Liaison Technician | Mobile Examiner | Patient Service Technician (PST) | Phlebotomist | Phlebotomy Technician | Registered Phlebotomist</t>
+  </si>
+  <si>
+    <t>Donor management system software | Electronic medical record EMR software | Iatric Systems MobiLab | JavaScript | Laboratory information system LIS | MEDITECH Blood Bank | MEDITECH Laboratory and Microbiology | MEDITECH software | Medical procedure coding software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Scheduling software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Education and Training | Psychology | Computers and Electronics | Medicine and Dentistry</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Problem Sensitivity | Written Comprehension | Oral Comprehension | Oral Expression | Deductive Reasoning | Speech Clarity | Finger Dexterity | Speech Recognition | Information Ordering | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Written Expression | Manual Dexterity | Selective Attention | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Telephone Conversations | Work With or Contribute to a Work Group or Team | Exposed to Disease or Infections | Consequence of Error | Time Pressure | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Deal With External Customers or the Public in General | Spend Time Standing | E-Mail | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Frequency of Decision Making | Dealing With Unpleasant, Angry, or Discourteous People | Indoors, Environmentally Controlled | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Walking or Running | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Cardiovascular Technologists and Technicians | Cytotechnologists | Diagnostic Medical Sonographers | Emergency Medical Technicians | Endoscopy Technicians | Histology Technicians | Histotechnologists | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Medical Records Specialists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Neurodiagnostic Technologists | Nurse Anesthetists | Nursing Assistants | Paramedics | Radiologic Technologists and Technicians | Surgical Assistants | Surgical Technologists | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Draw blood for tests, transfusions, donations, or research. May explain the procedure to patients and assist in the recovery of patients with adverse reactions.</t>
+  </si>
+  <si>
+    <t>Administer subcutaneous or intramuscular injects, in accordance with licensing restrictions. | Calibrate or maintain machines, such as those used for plasma collection. | Collect fluid or tissue samples, using appropriate collection procedures. | Collect specimens at specific time intervals for tests, such as those assessing therapeutic drug levels. | Conduct hemoglobin tests to ensure donor iron levels are normal. | Conduct standards tests, such as blood alcohol, blood culture, oral glucose tolerance, glucose screening, blood smears, or peak and trough drug levels tests. | Determine donor suitability, according to interview results, vital signs, and medical history. | Dispose of blood or other biohazard fluids or tissue, in accordance with applicable laws, standards, or policies. | Dispose of contaminated sharps, in accordance with applicable laws, standards, and policies. | Document route of specimens from collection to laboratory analysis and diagnosis. | Draw blood from arteries, using arterial collection techniques. | Draw blood from capillaries by dermal puncture, such as heel or finger stick methods. | Draw blood from veins by vacuum tube, syringe, or butterfly venipuncture methods. | Enter patient, specimen, insurance, or billing information into computer. | Explain fluid or tissue collection procedures to patients. | Match laboratory requisition forms to specimen tubes. | Monitor blood or plasma donors during and after procedures to ensure health, safety, and comfort. | Organize or clean blood-drawing trays, ensuring that all instruments are sterile and all needles, syringes, or related items are of first-time use. | Process blood or other fluid samples for further analysis by other medical professionals. | Provide sample analysis results to physicians to assist diagnosis. | Serve refreshments to donors to ensure absorption of sugar into their systems. | Train other medical personnel in phlebotomy or laboratory techniques. | Transport specimens or fluid samples from collection sites to laboratories.</t>
+  </si>
+  <si>
+    <t>31-9099.00</t>
+  </si>
+  <si>
+    <t>Healthcare Support Workers, All Other</t>
+  </si>
+  <si>
+    <t>Clinical Aide | Dialysis Aide | Health Aide | Healthcare Support Worker | Hospital Attendant | Patient Care Assistant | Patient Transporter | Rehabilitation Aide | Sterile Supply Aide | Ward Assistant</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Medicine and Dentistry | English Language | Psychology | Computers and Electronics | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Static Strength | Trunk Strength | Stamina</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Spend Time Walking or Running | Spend Time Bending or Twisting Your Body | Importance of Repeating Same Tasks | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Nursing Assistants | Orderlies | Home Health Aides | Personal Care Aides | Psychiatric Aides | Medical Assistants | Dental Assistants | Physical Therapist Aides | Occupational Therapy Aides | Pharmacy Aides | Medical Equipment Preparers | Phlebotomists | Endoscopy Technicians | Speech-Language Pathology Assistants | Veterinary Assistants and Laboratory Animal Caretakers | Licensed Practical and Licensed Vocational Nurses | Registered Nurses | Health Technologists and Technicians, All Other | Medical Records Specialists | Patient Representatives</t>
+  </si>
+  <si>
+    <t>All healthcare support workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Provide healthcare support services in roles not classified separately. | Assist patients with mobility, positioning, transport, and daily activities. | Prepare examination and treatment rooms and stock necessary supplies. | Clean, disinfect, and sterilize instruments, equipment, and surfaces. | Measure and record vital signs, intake and output, and basic observations. | Transport patients, specimens, supplies, and equipment within the facility. | Assist clinical staff during examinations, treatments, and procedures. | Answer patient calls and respond to routine requests for assistance. | Maintain inventories and restock treatment areas and supply rooms. | Follow infection control, safety, and patient privacy procedures. | Document care activities and report changes in patient condition. | Assist with admissions, discharges, and room turnover. | Handle and dispose of soiled linens, waste, and hazardous materials. | Provide comfort, reassurance, and companionship to patients and families.</t>
+  </si>
+  <si>
+    <t>31-9099.01</t>
+  </si>
+  <si>
+    <t>Speech-Language Pathology Assistants</t>
+  </si>
+  <si>
+    <t>Communication Assistant | Speech Assistant | Speech Paraeducator | Speech Pathologist Assistant | Speech Therapy Assistant | Speech-Language Assistant | Speech-Language Pathologist Assistant (SLPA) | Speech-Language Pathologists Assistant (SLPA) | Speech-Language Pathology Assistant (SLPA) | Speech-Language Technician</t>
+  </si>
+  <si>
+    <t>Adobe Audition | Biofeedback software | Bungalow Software Aphasia Tutor | ELR Software eLr Extra Language Resources | Email software | KayPENTAX Multi-Speech | Language analysis software | Learning Fundamentals Speech Visualization | Micro Video Video Voice Speech Training System | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | Propeller Multimedia React2 | Signal analysis software | Speech analysis software | Text to speech software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Monitoring | Critical Thinking | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>English Language | Education and Training | Therapy and Counseling | Psychology | Customer and Personal Service | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Written Comprehension | Written Expression | Problem Sensitivity | Information Ordering | Near Vision | Inductive Reasoning | Deductive Reasoning | Hearing Sensitivity | Originality | Fluency of Ideas | Time Sharing | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | E-Mail | Physical Proximity | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Telephone Conversations | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Sitting | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Advanced Practice Psychiatric Nurses | Audiologists | Cardiologists | Cardiovascular Technologists and Technicians | Clinical Nurse Specialists | Emergency Medicine Physicians | Hearing Aid Specialists | Low Vision Therapists, Orientation and Mobility Specialists, and Vision Rehabilitation Therapists | Medical Assistants | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Pediatric Surgeons | Physical Therapist Aides | Physical Therapist Assistants | Psychiatric Aides | Psychiatric Technicians | Recreational Therapists | Rehabilitation Counselors | Speech-Language Pathologists</t>
+  </si>
+  <si>
+    <t>Assist speech-language pathologists in the assessment and treatment of speech, language, voice, and fluency disorders. Implement speech and language programs or activities as planned and directed by speech-language pathologists. Monitor the use of alternative communication devices and systems.</t>
+  </si>
+  <si>
+    <t>Assist speech-language pathologists in the conduct of client screenings or assessments of language, voice, fluency, articulation, or hearing. | Assist speech-language pathologists in the conduct of speech-language research projects. | Assist speech-language pathologists in the remediation or development of speech and language skills. | Collect and compile data to document clients' performance or assess program quality. | Conduct in-service training sessions, or family and community education programs. | Document clients' progress toward meeting established treatment objectives. | Implement treatment plans or protocols as directed by speech-language pathologists. | Perform support duties, such as preparing materials, keeping records, maintaining supplies, and scheduling activities. | Prepare charts, graphs, or other visual displays to communicate clients' performance information. | Select or prepare speech-language instructional materials. | Test or maintain equipment to ensure correct performance.</t>
+  </si>
+  <si>
+    <t>31-9099.02</t>
+  </si>
+  <si>
+    <t>Endoscopy Technicians</t>
+  </si>
+  <si>
+    <t>Certified Endo Tech (Certified Endoscopy Technician) | Certified Endoscopic Reprocessor (CER) | Certified Flexible Endoscope Reprocessor (CFER) | Certified Flexible Endoscopy Reprocessor (CFER) | Endoscope Technician (Endoscope Tech) | Endoscopy Specialty Technician (Endoscopy Specialty Tech) | Endoscopy Technician (Endoscopy Tech) | GI Tech (Gastrointestinal Technician) | Procedural Assistant (Procedural Asst) | Scope Tech (Scope Technician)</t>
+  </si>
+  <si>
+    <t>Email software | MEDITECH software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Patient electronic medical record EMR software | Scheduling software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Critical Thinking | Writing | Speaking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Medicine and Dentistry | Education and Training | Computers and Electronics | Production and Processing</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Oral Comprehension | Oral Expression | Written Comprehension | Arm-Hand Steadiness | Finger Dexterity | Deductive Reasoning | Information Ordering | Manual Dexterity | Speech Recognition | Speech Clarity | Category Flexibility | Written Expression | Control Precision | Selective Attention | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Contact With Others | Spend Time Standing | Exposed to Disease or Infections | Physical Proximity | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Exposed to Contaminants | Importance of Repeating Same Tasks | Consequence of Error | Spend Time Making Repetitive Motions | E-Mail | Time Pressure | Telephone Conversations | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Anesthesiologist Assistants | Cardiologists | Cardiovascular Technologists and Technicians | Diagnostic Medical Sonographers | Medical Assistants | Medical Equipment Preparers | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Neurodiagnostic Technologists | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Radiation Therapists | Radiologic Technologists and Technicians | Radiologists | Respiratory Therapists | Surgical Assistants | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Maintain a sterile field to provide support for physicians and nurses during endoscopy procedures. Prepare and maintain instruments and equipment. May obtain specimens.</t>
+  </si>
+  <si>
+    <t>Assist physicians or registered nurses in the conduct of endoscopic procedures. | Attend in-service training to validate or refresh basic professional skills. | Clean, disinfect, or calibrate scopes or other endoscopic instruments according to manufacturer recommendations and facility standards. | Collect specimens from patients, using standard medical procedures. | Conduct in-service training sessions to disseminate information regarding equipment or instruments. | Maintain inventories of endoscopic equipment and supplies. | Maintain or repair endoscopic equipment. | Perform safety checks to verify proper equipment functioning. | Place devices, such as blood pressure cuffs, pulse oximeter sensors, nasal cannulas, surgical cautery pads, and cardiac monitoring electrodes, on patients to monitor vital signs. | Position or transport patients in accordance with instructions from medical personnel. | Prepare suites or rooms according to endoscopic procedure requirements. | Read current literature, talk with colleagues, or participate in professional organizations or conferences to keep abreast of developments in endoscopy.</t>
+  </si>
+  <si>
+    <t>33-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Correctional Officers</t>
+  </si>
+  <si>
+    <t>Correctional Officer Captain | Correctional Supervisor</t>
+  </si>
+  <si>
+    <t>3M Electronic Monitoring | Email software | Guardian RFID | Jail management software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Speaking | Reading Comprehension | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | Administration and Management | Psychology | English Language | Administrative | Computers and Electronics | Education and Training | Personnel and Human Resources | Customer and Personal Service | Sociology and Anthropology | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Written Comprehension | Written Expression | Inductive Reasoning | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Information Ordering | Auditory Attention | Static Strength | Reaction Time | Selective Attention | Perceptual Speed | Flexibility of Closure | Trunk Strength | Explosive Strength | Stamina | Response Orientation | Time Sharing | Category Flexibility | Fluency of Ideas | Gross Body Equilibrium</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Health and Safety of Other Workers | Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results | Dealing with Violent or Physically Aggressive People | Time Pressure | Freedom to Make Decisions | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Public Speaking | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Exposed to Disease or Infections | Importance of Repeating Same Tasks | Outdoors, Exposed to All Weather Conditions | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Bailiffs | Correctional Officers and Jailers | Detectives and Criminal Investigators | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Medical and Health Services Managers | Police and Sheriff's Patrol Officers | Probation Officers and Correctional Treatment Specialists | Rehabilitation Counselors | Residential Advisors | Social and Community Service Managers | Social and Human Service Assistants | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of correctional officers and jailers.</t>
+  </si>
+  <si>
+    <t>Carry injured offenders or employees to safety and provide emergency first aid when necessary. | Complete administrative paperwork or supervise the preparation or maintenance of records, forms, or reports. | Conduct evaluations of employees' performance. | Conduct roll calls of correctional officers. | Convey correctional officers' or inmates' complaints to superiors. | Develop work or security procedures. | Examine incoming or outgoing mail to ensure conformance with regulations. | Instruct employees or provide on-the-job training. | Maintain knowledge of, comply with, and enforce all institutional policies, rules, procedures, and regulations. | Maintain order, discipline, and security within assigned areas in accordance with relevant rules, regulations, policies, and laws. | Monitor behavior of subordinates to ensure alert, courteous, and professional behavior toward inmates, parolees, fellow employees, visitors, and the public. | Rate behavior of inmates, promoting acceptable attitudes and behaviors to those with low ratings. | Resolve problems between inmates. | Respond to emergencies, such as escapes. | Restrain, secure, or control offenders, using chemical agents, firearms, or other weapons of force as necessary. | Review offender information to identify issues that require special attention. | Set up employee work schedules. | Supervise activities, such as searches, shakedowns, riot control, or institutional tours. | Supervise and direct the work of correctional officers to ensure the safe custody, discipline, and welfare of inmates. | Supervise or perform searches of inmates or their quarters to locate contraband items. | Supervise or provide security for offenders performing tasks, such as construction, maintenance, laundry, food service, or other industrial or agricultural operations. | Take, receive, or check periodic inmate counts. | Transfer or transport offenders on foot or by driving vehicles, such as trailers, vans, or buses.</t>
+  </si>
+  <si>
+    <t>33-1012.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Police and Detectives</t>
+  </si>
+  <si>
+    <t>Captain | Deputy Sheriff | Detective Sergeant | Lieutenant | Patrol Sergeant | Police Captain | Police Chief | Police Lieutenant | Police Sergeant | Shift Supervisor</t>
+  </si>
+  <si>
+    <t>Computer aided composite drawing software | Computer aided dispatch software | Corel WordPerfect Office Suite | Crime mapping software | DesignWare 3D EyeWitness | Email software | Integrated Automated Fingerprint Identification System IAFIS | Law enforcement information databases | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | National Crime Information Center (NCIC) database | National Integrated Ballistics Information Network NIBIN | Scheduling software | SmartDraw Legal | Spillman Technologies Records Management | The CAD Zone The Crime Zone</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening | Reading Comprehension | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | Customer and Personal Service | Administration and Management | English Language | Psychology | Sociology and Anthropology | Therapy and Counseling | Education and Training | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Problem Sensitivity | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Speech Recognition | Speech Clarity | Near Vision | Selective Attention | Category Flexibility | Flexibility of Closure | Fluency of Ideas | Far Vision | Manual Dexterity | Arm-Hand Steadiness | Perceptual Speed | Speed of Closure | Memorization | Originality</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Contact With Others | Impact of Decisions on Co-workers or Company Results | In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making | Freedom to Make Decisions | Dealing With Unpleasant, Angry, or Discourteous People | Work With or Contribute to a Work Group or Team | Outdoors, Exposed to All Weather Conditions | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Conflict Situations | Work Outcomes and Results of Other Workers | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Consequence of Error | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Written Letters and Memos | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Disease or Infections | Exposed to Very Hot or Cold Temperatures | Time Pressure</t>
+  </si>
+  <si>
+    <t>Bailiffs | Chief Executives | Compliance Officers | Coroners | Correctional Officers and Jailers | Detectives and Criminal Investigators | Emergency Management Directors | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Security Workers | General and Operations Managers | Intelligence Analysts | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Probation Officers and Correctional Treatment Specialists | Public Safety Telecommunicators | Security Guards | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of members of police force.</t>
+  </si>
+  <si>
+    <t>Conduct raids and order detention of witnesses and suspects for questioning. | Cooperate with court personnel and officials from other law enforcement agencies and testify in court, as necessary. | Develop, implement, and revise departmental policies and procedures. | Direct collection, preparation, and handling of evidence and personal property of prisoners. | Direct release or transfer of prisoners. | Discipline staff for violation of department rules and regulations. | Explain police operations to subordinates to assist them in performing their job duties. | Inform personnel of changes in regulations and policies, implications of new or amended laws, and new techniques of police work. | Inspect facilities, supplies, vehicles, and equipment to ensure conformance to standards. | Investigate and resolve personnel problems within organization and charges of misconduct against staff. | Maintain logs, prepare reports, and direct the preparation, handling, and maintenance of departmental records. | Meet with civic, educational, and community groups to develop community programs and events, and to discuss law enforcement subjects. | Monitor and evaluate the job performance of subordinates, and authorize promotions and transfers. | Prepare budgets and manage expenditures of department funds. | Prepare news releases and respond to police correspondence. | Prepare work schedules and assign duties to subordinates. | Requisition and issue equipment and supplies. | Review contents of written orders to ensure adherence to legal requirements. | Supervise and coordinate the investigation of criminal cases, offering guidance and expertise to investigators, and ensuring that procedures are conducted in accordance with laws and regulations. | Train staff in proper police work procedures.</t>
+  </si>
+  <si>
+    <t>33-1021.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Firefighting and Prevention Workers</t>
+  </si>
+  <si>
+    <t>Engine Boss | Fire Battalion Chief | Fire Captain | Fire Chief | Fire Lieutenant | Fire Marshal | Fire Prevention Chief | Fire Suppression Captain | Forest Fire Specialist Supervisor | Section Forest Fire Warden</t>
+  </si>
+  <si>
+    <t>Affiliated Computer Services ACS FIREHOUSE | BIO-key FireRMS | BehavePlus | Computer aided dispatch software | Corel WordPerfect Office Suite | ESRI ArcView | Email software | FARSITE | Fire incident reporting systems | FlamMap | Geographic information system GIS software | Geographic information system GIS systems | IBM Lotus 1-2-3 | Incident command system ICS software | Mapping software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Plume modeling software | Resource Ordering and Statusing System ROSS | Web browser software | Wildland Fire Assessment System WFAS</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Reading Comprehension | Speaking | Monitoring | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | Education and Training | Building and Construction | Administration and Management | English Language | Mechanical | Law and Government | Personnel and Human Resources | Administrative | Medicine and Dentistry | Psychology | Chemistry | Transportation | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Problem Sensitivity | Near Vision | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Written Expression | Information Ordering | Speech Recognition | Speech Clarity | Fluency of Ideas | Category Flexibility | Originality | Perceptual Speed | Selective Attention | Manual Dexterity | Trunk Strength | Far Vision | Explosive Strength | Static Strength | Arm-Hand Steadiness | Visualization | Finger Dexterity | Time Sharing | Flexibility of Closure | Speed of Closure | Gross Body Equilibrium | Extent Flexibility | Multilimb Coordination | Control Precision | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Telephone Conversations | Deal With External Customers or the Public in General | E-Mail | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Consequence of Error | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Frequency of Decision Making | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Physical Proximity | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Indoors, Environmentally Controlled | Exposed to Hazardous Conditions | Exposed to Disease or Infections | Exposed to Extremely Bright or Inadequate Lighting Conditions | Written Letters and Memos | Time Pressure | Level of Competition</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialists | Construction and Building Inspectors | Emergency Management Directors | Fire Inspectors and Investigators | Fire-Prevention and Protection Engineers | Firefighters | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Forest Fire Inspectors and Prevention Specialists | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Police and Sheriff's Patrol Officers | Ship Engineers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of workers engaged in firefighting and fire prevention and control.</t>
+  </si>
+  <si>
+    <t>Analyze burn conditions and results, and prepare postburn reports. | Assess nature and extent of fire, condition of building, danger to adjacent buildings, and water supply status to determine crew or company requirements. | Assign firefighters to jobs at strategic locations to facilitate rescue of persons and maximize application of extinguishing agents. | Communicate fire details to superiors, subordinates, or interagency dispatch centers, using two-way radios. | Direct firefighters in station maintenance duties, and participate in these duties. | Direct investigation of cases of suspected arson, hazards, and false alarms and submit reports outlining findings. | Direct the training of firefighters, assigning of instructors to training classes, and providing of supervisors with reports on training progress and status. | Drive crew carriers to transport firefighters to fire sites. | Evaluate fire station procedures to ensure efficiency and enforcement of departmental regulations. | Evaluate size, location, and condition of fires. | Evaluate the performance of assigned firefighting personnel. | Inspect and test new and existing fire protection systems, fire detection systems, and fire safety equipment to ensure that they are operating properly. | Inspect stations, uniforms, equipment, or recreation areas to ensure compliance with safety standards, taking corrective action as necessary. | Instruct and drill fire department personnel in assigned duties, including firefighting, medical care, hazardous materials response, fire prevention, and related subjects. | Maintain fire suppression equipment in good condition, checking equipment periodically to ensure that it is ready for use. | Maintain knowledge of fire laws and fire prevention techniques and tactics. | Maintain required maps and records. | Monitor fire suppression expenditures to ensure that they are necessary and reasonable. | Participate in creating fire safety guidelines and evacuation schemes for nonresidential buildings. | Perform administrative duties, such as compiling and maintaining records, completing forms, preparing reports, or composing correspondence. | Perform maintenance and minor repairs on firefighting equipment, including vehicles, and write and submit proposals to modify, replace, and repair equipment. | Plan, direct, and supervise prescribed burn projects. | Provide emergency medical services as required, and perform light to heavy rescue functions at emergencies. | Recommend equipment modifications or new equipment purchases. | Recommend personnel actions related to disciplinary procedures, performance, leaves of absence, and grievances. | Recruit or hire firefighting personnel. | Schedule employee work assignments and set work priorities. | Serve as a working leader of an engine, hand, helicopter, or prescribed fire crew of three or more firefighters. | Study and interpret fire safety codes to establish procedures for issuing permits to handle hazardous or flammable substances. | Supervise and participate in the inspection of properties to ensure that they are in compliance with applicable fire codes, ordinances, laws, regulations, and standards.</t>
+  </si>
+  <si>
+    <t>33-1091.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Security Workers</t>
+  </si>
+  <si>
+    <t>Campus Safety Chief | Public Safety Manager | Public Safety Supervisor | Security Chief | Security Director | Security Guard Supervisor | Security Lieutenant | Security Shift Supervisor | Security Supervisor | Shift Supervisor</t>
+  </si>
+  <si>
+    <t>Employee scheduling software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle software | SAP business and customer relations management software | Time and attendance software</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Speaking | Critical Thinking | Monitoring | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Administration and Management | Customer and Personal Service | Personnel and Human Resources | Law and Government | English Language | Administrative | Education and Training | Computers and Electronics | Psychology | Telecommunications | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Inductive Reasoning | Near Vision | Far Vision | Speech Recognition | Deductive Reasoning | Written Comprehension | Written Expression | Flexibility of Closure | Speech Clarity | Information Ordering | Selective Attention | Speed of Closure | Perceptual Speed | Fluency of Ideas | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Contact With Others | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Work Outcomes and Results of Other Workers | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Physical Proximity | Importance of Repeating Same Tasks | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Production and Operating Workers | Police and Sheriff's Patrol Officers | Retail Loss Prevention Specialists | Security Guards | Security Management Specialists | Security Managers | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of security workers and security guards.</t>
+  </si>
+  <si>
+    <t>Advise employees in handling problems or resolving complaints from customers, tenants, detainees, or other persons. | Apprehend or evict trespassers, rule violators, or other security threats from the premises. | Assign security personnel to posts or patrols. | Call police or fire departments in cases of emergency, such as fire, bomb threats, and presence of unauthorized persons. | Develop and document security procedures, policies, or standards. | Explain company policies and procedures to staff using oral or written communication. | Inspect and adjust security equipment to ensure it is operational or to detect evidence of tampering. | Investigate disturbances on the premises, such as security alarms, altercations, and suspicious activity. | Log items distributed to persons, such as keys and key cards. | Monitor and authorize entry of employees, visitors, or other persons. | Monitor closed-circuit television cameras. | Monitor the behavior of security employees to ensure adherence to quality standards, deadlines, or procedures. | Order materials or supplies, such as keys, uniforms, and badges. | Patrol the premises to prevent or detect intrusion, protect property, or preserve order. | Recruit, interview, and hire security personnel. | Schedule training or drills for emergencies, such as fires, bombs, and other threats. | Screen individuals and belongings to prevent passage of prohibited materials using walkthrough detectors, wands, or bag searches. | Secure entrances and exits by locking doors and gates. | Train security personnel on protective procedures, first aid, fire safety, and other duties. | Write and present department budgets to upper management or other stakeholders. | Write reports documenting observations made while on patrol.</t>
+  </si>
+  <si>
+    <t>33-1099.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Protective Service Workers, All Other</t>
+  </si>
+  <si>
+    <t>Chief of Security | Guard Supervisor | Patrol Supervisor | Protective Services Supervisor | Safety Supervisor | Security Shift Supervisor | Security Supervisor | Shift Commander | Watch Commander | Loss Prevention Supervisor</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Scheduling software</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Administration and Management | Customer and Personal Service | Law and Government | English Language | Personnel and Human Resources | Education and Training | Psychology | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Deal With External Customers or the Public in General | Telephone Conversations | Consequence of Error | Frequency of Decision Making | Health and Safety of Other Workers | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Dealing with Violent or Physically Aggressive People | Spend Time Standing | Spend Time Walking or Running | Exposed to Hazardous Conditions | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Time Pressure | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition | Freedom to Make Decisions | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Security Workers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Firefighting and Prevention Workers | Security Guards | Retail Loss Prevention Specialists | Gambling Surveillance Officers and Gambling Investigators | Private Detectives and Investigators | Transportation Security Screeners | Correctional Officers and Jailers | Police and Sheriff's Patrol Officers | Detectives and Criminal Investigators | Protective Service Workers, All Other | Security Managers | Emergency Management Directors | Compliance Officers | Occupational Health and Safety Specialists | Loss Prevention Managers | General and Operations Managers | Security Management Specialists</t>
+  </si>
+  <si>
+    <t>All protective service supervisors not listed separately above.</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate protective service workers in roles not classified separately. | Assign posts, patrols, and duty schedules to subordinate personnel. | Train staff in security procedures, emergency response, and use of equipment. | Inspect posts and patrols to verify adherence to procedures and standards. | Investigate incidents, security breaches, and complaints and prepare reports. | Coordinate responses to emergencies with police, fire, and medical services. | Evaluate employee performance and recommend personnel actions. | Develop and update post orders, emergency plans, and standard procedures. | Monitor surveillance systems, alarms, and access control equipment. | Maintain records of incidents, patrols, equipment, and personnel. | Enforce compliance with regulations, licensing, and company policy. | Conduct risk assessments and recommend security improvements. | Manage supplies, uniforms, and equipment for the assigned unit. | Interact with clients, tenants, and the public to resolve security concerns.</t>
+  </si>
+  <si>
+    <t>33-2011.00</t>
+  </si>
+  <si>
+    <t>Firefighters</t>
+  </si>
+  <si>
+    <t>Fire Engineer | Fire Equipment Operator | Fire Fighter | Fire Management Specialist | Fire Technician (Fire Tech) | Firefighter | Forest Fire Suppression Specialist | Forestry Fire Technician (Forestry Fire Tech) | Hot Shot | Wildland Firefighter</t>
+  </si>
+  <si>
+    <t>Affiliated Computer Services ACS FIREHOUSE | Corel WordPerfect Office Suite | Email software | Fire incident reporting systems | Geographic information system GIS software | Incident command system ICS software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Plume modeling software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Active Learning | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | Education and Training | Building and Construction | English Language | Mechanical | Medicine and Dentistry | Telecommunications | Administration and Management | Transportation | Law and Government | Chemistry | Psychology | Mathematics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Oral Expression | Deductive Reasoning | Arm-Hand Steadiness | Static Strength | Far Vision | Stamina | Inductive Reasoning | Near Vision | Speech Clarity | Control Precision | Multilimb Coordination | Flexibility of Closure | Information Ordering | Trunk Strength | Dynamic Strength | Reaction Time | Manual Dexterity | Speech Recognition | Auditory Attention | Perceptual Speed | Extent Flexibility | Written Comprehension | Spatial Orientation | Visualization | Depth Perception | Visual Color Discrimination | Explosive Strength | Selective Attention | Speed of Closure | Category Flexibility | Gross Body Coordination | Written Expression | Gross Body Equilibrium | Response Orientation | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Deal With External Customers or the Public in General | Outdoors, Exposed to All Weather Conditions | Health and Safety of Other Workers | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | In an Enclosed Vehicle or Operate Enclosed Equipment | Telephone Conversations | Consequence of Error | Exposed to Hazardous Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Exposed to Extremely Bright or Inadequate Lighting Conditions | Exposed to Disease or Infections | Work Outcomes and Results of Other Workers | E-Mail | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to Hazardous Conditions | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Cramped Work Space, Awkward Positions | Level of Competition | Time Pressure | Exposed to High Places | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Electrical Power-Line Installers and Repairers | Emergency Management Directors | Emergency Medical Technicians | Fire Inspectors and Investigators | Fire-Prevention and Protection Engineers | First-Line Supervisors of Firefighting and Prevention Workers | Forest Fire Inspectors and Prevention Specialists | Forest and Conservation Technicians | Forest and Conservation Workers | Hazardous Materials Removal Workers | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Paramedics | Sailors and Marine Oilers | Security Guards | Ship Engineers | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Control and extinguish fires or respond to emergency situations where life, property, or the environment is at risk. Duties may include fire prevention, emergency medical service, hazardous material response, search and rescue, and disaster assistance.</t>
+  </si>
+  <si>
+    <t>Administer first aid and cardiopulmonary resuscitation to injured persons or provide emergency medical care such as basic or advanced life support. | Assess fires and situations and report conditions to superiors to receive instructions, using two-way radios. | Clean and maintain fire stations and fire fighting equipment and apparatus. | Collaborate with other firefighters as a member of a firefighting crew. | Collaborate with police to respond to accidents, disasters, and arson investigation calls. | Create openings in buildings for ventilation or entrance, using axes, chisels, crowbars, electric saws, or core cutters. | Dress with equipment such as fire-resistant clothing and breathing apparatus. | Drive and operate fire fighting vehicles and equipment. | Extinguish flames and embers to suppress fires, using shovels or engine- or hand-driven water or chemical pumps. | Inform and educate the public on fire prevention. | Inspect buildings for fire hazards and compliance with fire prevention ordinances, testing and checking smoke alarms and fire suppression equipment as necessary. | Inspect fire sites after flames have been extinguished to ensure that there is no further danger. | Maintain contact with fire dispatchers at all times to notify them of the need for additional firefighters and supplies, or to detail any difficulties encountered. | Maintain knowledge of current firefighting practices by participating in drills and by attending seminars, conventions, and conferences. | Move toward the source of a fire, using knowledge of types of fires, construction design, building materials, and physical layout of properties. | Operate pumps connected to high-pressure hoses. | Orient self in relation to fire, using compass and map, and collect supplies and equipment dropped by parachute. | Participate in fire drills and demonstrations of fire fighting techniques. | Participate in physical training activities to maintain a high level of physical fitness. | Patrol burned areas after fires to locate and eliminate hot spots that may restart fires. | Position and climb ladders to gain access to upper levels of buildings, or to rescue individuals from burning structures. | Prepare written reports that detail specifics of fire incidents. | Protect property from water and smoke, using waterproof salvage covers, smoke ejectors, and deodorants. | Rescue survivors from burning buildings, accident sites, and water hazards. | Respond to fire alarms and other calls for assistance, such as automobile and industrial accidents. | Salvage property by removing broken glass, pumping out water, and ventilating buildings to remove smoke. | Search to locate fire survivors. | Select and attach hose nozzles, depending on fire type, and direct streams of water or chemicals onto fires. | Take action to contain any hazardous chemicals that could catch fire, leak, or spill. | Train new employees to control and suppress fires.</t>
+  </si>
+  <si>
+    <t>33-2021.00</t>
+  </si>
+  <si>
+    <t>Fire Inspectors and Investigators</t>
+  </si>
+  <si>
+    <t>Arson Investigator | Fire Code Inspector | Fire Inspector | Fire Investigator | Fire Official | Fire Prevention Inspector | Fire Prevention Specialist | Fire Protection Specialist | Fire Safety Inspector | Fire Safety Specialist</t>
+  </si>
+  <si>
+    <t>Code database software | Consolidated Model of Fire and Smoke Transport CFAST | Email software | Fire Dynamics Software FDS | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | National Fire Incident Reporting System NFIRS | Web browser software | Xerox Government systems FIREHOUSE Software</t>
+  </si>
+  <si>
+    <t>Active Listening | Writing | Speaking | Critical Thinking | Reading Comprehension | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | Building and Construction | Law and Government | Education and Training | English Language | Administration and Management</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Written Comprehension | Written Expression | Deductive Reasoning | Oral Expression | Inductive Reasoning | Information Ordering | Near Vision | Flexibility of Closure | Category Flexibility | Speech Clarity | Speech Recognition | Selective Attention | Fluency of Ideas | Visual Color Discrimination | Far Vision | Originality</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | E-Mail | In an Enclosed Vehicle or Operate Enclosed Equipment | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Outdoors, Exposed to All Weather Conditions | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Written Letters and Memos | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Not Environmentally Controlled | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aviation Inspectors | Construction and Building Inspectors | Emergency Management Directors | Environmental Compliance Inspectors | Environmental Science and Protection Technicians, Including Health | Fire-Prevention and Protection Engineers | Firefighters | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Security Workers | Forest Fire Inspectors and Prevention Specialists | Government Property Inspectors and Investigators | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Security Guards | Security Management Specialists | Security Managers | Security and Fire Alarm Systems Installers | Transit and Railroad Police | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Inspect buildings to detect fire hazards and enforce local ordinances and state laws, or investigate and gather facts to determine cause of fires and explosions.</t>
+  </si>
+  <si>
+    <t>Analyze evidence and other information to determine probable cause of fire or explosion. | Arrange for the replacement of defective fire fighting equipment and for repair of fire alarm and sprinkler systems, making minor repairs such as servicing fire extinguishers when feasible. | Attend training classes to maintain current knowledge of fire prevention, safety, and firefighting procedures. | Conduct fire code compliance follow-ups to ensure that corrective actions have been taken in cases where violations were found. | Conduct fire exit drills to monitor and evaluate evacuation procedures. | Conduct inspections and acceptance testing of newly installed fire protection systems. | Conduct internal investigation to determine negligence and violation of laws and regulations by fire department employees. | Coordinate efforts with other organizations, such as law enforcement agencies. | Develop and coordinate fire prevention programs, such as false alarm billing, fire inspection reporting, and hazardous materials management. | Develop or review fire exit plans. | Dust evidence or portions of fire scenes for latent fingerprints. | Examine fire sites and collect evidence such as glass, metal fragments, charred wood, and accelerant residue for use in determining the cause of a fire. | Identify corrective actions necessary to bring properties into compliance with applicable fire codes, laws, regulations, and standards, and explain these measures to property owners or their representatives. | Inspect and test fire protection or fire detection systems to verify that such systems are installed in accordance with appropriate laws, codes, ordinances, regulations, and standards. | Inspect buildings to locate hazardous conditions and fire code violations, such as accumulations of combustible material, electrical wiring problems, and inadequate or non-functional fire exits. | Inspect properties that store, handle, and use hazardous materials to ensure compliance with laws, codes, and regulations, and issue hazardous materials permits to facilities found in compliance. | Instruct children about the dangers of fire. | Issue permits for public assemblies. | Package collected pieces of evidence in securely closed containers, such as bags, crates, or boxes, to protect them. | Photograph damage and evidence related to causes of fires or explosions to document investigation findings. | Prepare and maintain reports of investigation results, and records of convicted arsonists and arson suspects. | Recommend changes to fire prevention, inspection, and fire code endorsement procedures. | Review blueprints and plans for new or remodeled buildings to ensure the structures meet fire safety codes. | Subpoena and interview witnesses, property owners, and building occupants to obtain information and sworn testimony. | Supervise staff, training them, planning their work, and evaluating their performance. | Teach fire investigation techniques to other firefighter personnel. | Teach public education programs on fire safety and prevention. | Test sites and materials to establish facts, such as burn patterns and flash points of materials, using test equipment. | Testify in court cases involving fires, suspected arson, and false alarms. | Write detailed reports of fire inspections performed, fire code violations observed, and corrective recommendations offered.</t>
+  </si>
+  <si>
+    <t>33-2022.00</t>
+  </si>
+  <si>
+    <t>Forest Fire Inspectors and Prevention Specialists</t>
+  </si>
+  <si>
+    <t>Fire Management Officer | Fire Operations Forester | Fire Prevention Officer | Fire Prevention Technician | Fire Technician | Forest Officer | Forest Patrolman | Forestry Patrolman | Wildfire Mitigation Specialist | Wildfire Prevention Specialist</t>
+  </si>
+  <si>
+    <t>Amazon Web Services AWS CloudFormation | Amazon Web Services AWS software | Ansible software | Docker | Facebook | Fire incident reporting systems | Git | Kubernetes | Linux | Mapping software | Microsoft Active Server Pages ASP | Microsoft Azure software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft SharePoint | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Object oriented development environment software | Perforce software | Puppet | Relational database software | Salesforce software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Monitoring | Learning Strategies | Reading Comprehension | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>Administration and Management | Customer and Personal Service | Education and Training | Personnel and Human Resources | Public Safety and Security | Law and Government | Computers and Electronics | English Language | Transportation | Administrative | Mechanical | Communications and Media | Geography</t>
+  </si>
+  <si>
+    <t>Oral Expression | Problem Sensitivity | Oral Comprehension | Deductive Reasoning | Near Vision | Written Comprehension | Far Vision | Flexibility of Closure | Inductive Reasoning | Speech Clarity | Perceptual Speed | Written Expression | Speed of Closure | Information Ordering | Speech Recognition | Depth Perception | Multilimb Coordination | Selective Attention | Category Flexibility | Originality</t>
+  </si>
+  <si>
+    <t>Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Telephone Conversations | E-Mail | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition | Deal With External Customers or the Public in General | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Exposed to Contaminants | Determine Tasks, Priorities and Goals | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work Outcomes and Results of Other Workers | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Time Pressure | Consequence of Error | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Repeating Same Tasks | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Emergency Management Directors | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Fire Inspectors and Investigators | Fire-Prevention and Protection Engineers | Firefighters | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Firefighting and Prevention Workers | Forest and Conservation Technicians | Forest and Conservation Workers | Foresters | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Public Safety Telecommunicators | Range Managers | Security Guards | Transit and Railroad Police | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Enforce fire regulations, inspect forest for fire hazards, and recommend forest fire prevention or control measures. May report forest fires and weather conditions.</t>
+  </si>
+  <si>
+    <t>Administer regulations regarding sanitation, fire prevention, violation corrections, and related forest regulations. | Compile and report meteorological data, such as temperature, relative humidity, wind direction and velocity, and types of cloud formations. | Conduct wildland firefighting training. | Direct crews working on firelines during forest fires. | Direct maintenance and repair of firefighting equipment, or requisition new equipment. | Educate the public about fire safety and prevention. | Estimate sizes and characteristics of fires, and report findings to base camps by radio or telephone. | Examine and inventory firefighting equipment, such as axes, fire hoses, shovels, pumps, buckets, and fire extinguishers, to determine amount and condition. | Extinguish smaller fires with portable extinguishers, shovels, and axes. | Inspect camp sites to ensure that campers are in compliance with forest use regulations. | Inspect forest tracts and logging areas for fire hazards such as accumulated wastes or mishandling of combustibles, and recommend appropriate fire prevention measures. | Locate forest fires on area maps, using azimuth sighters and known landmarks. | Maintain records and logbooks. | Patrol assigned areas, looking for forest fires, hazardous conditions, and weather phenomena. | Relay messages about emergencies, accidents, locations of crew and personnel, and fire hazard conditions. | Restrict public access and recreational use of forest lands during critical fire seasons.</t>
+  </si>
+  <si>
+    <t>33-3011.00</t>
+  </si>
+  <si>
+    <t>Bailiffs</t>
+  </si>
+  <si>
+    <t>Bailiff | Court Bailiff | Court Constable | Court Deputy | Court Officer | Court Security Officer | Deputy Bailiff | Deputy Court Services Sheriff | Security Officer</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Case management system software | Corel WordPerfect Office Suite | Court docket management software | Email software | IBM Lotus Notes | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | National Crime Information Center (NCIC) database | State crime information databases | Statistics software | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Active Listening | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | English Language | Customer and Personal Service | Psychology</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Expression | Selective Attention | Speech Clarity | Oral Comprehension | Speech Recognition | Near Vision | Deductive Reasoning | Trunk Strength | Static Strength | Information Ordering | Inductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Dealing With Unpleasant, Angry, or Discourteous People | Physical Proximity | Frequency of Decision Making | Freedom to Make Decisions | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail</t>
+  </si>
+  <si>
+    <t>Administrative Law Judges, Adjudicators, and Hearing Officers | Arbitrators, Mediators, and Conciliators | Coroners | Correctional Officers and Jailers | Court Reporters and Simultaneous Captioners | Court, Municipal, and License Clerks | Customs and Border Protection Officers | Detectives and Criminal Investigators | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Judges, Magistrate Judges, and Magistrates | Judicial Law Clerks | Lawyers | Legal Secretaries and Administrative Assistants | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Probation Officers and Correctional Treatment Specialists | Security Guards | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Maintain order in courts of law.</t>
+  </si>
+  <si>
+    <t>Announce entrance of judge. | Arrest persons in court when arrest warrants have been issued. | Check courtroom for security and cleanliness and assure availability of sundry supplies, such as notepads, for use by judge, jurors, and attorneys. | Enforce courtroom rules of behavior and warn persons not to smoke or disturb court procedure. | Escort prisoners to and from courthouse and maintain custody of prisoners during court proceedings. | Guard lodging of sequestered jury. | Maintain court docket. | Maintain order in courtroom during trial and guard jury from outside contact. | Provide assistance to the public, such as directions to court offices. | Provide jury escort to restaurant and other areas outside of courtroom to prevent jury contact with public. | Provide security by patrolling interior and exterior of courthouse and escorting judges and other court employees. | Report need for police or medical assistance to sheriff's office. | Screen persons entering courthouse using magnetometers, x-ray machines, and other devices to collect and retain unauthorized firearms and other contraband. | Screen, control, and handle evidence and exhibits during court proceedings. | Stop people from entering courtroom while judge charges jury.</t>
+  </si>
+  <si>
+    <t>33-3012.00</t>
+  </si>
+  <si>
+    <t>Correctional Officers and Jailers</t>
+  </si>
+  <si>
+    <t>Booking Officer | Community Services Officer (CSO) | Correctional Officer | Corrections Officer (CO) | Deputy Jailer | Detention Deputy | Detention Officer | Jail Officer | Jailer | Jailor</t>
+  </si>
+  <si>
+    <t>3M Electronic Monitoring | Adobe Acrobat | Corrections housing software | Facebook | Guardian RFID | Jail management software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Speaking | Critical Thinking | Reading Comprehension | Active Learning | Learning Strategies | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | English Language | Law and Government | Customer and Personal Service | Administration and Management | Computers and Electronics | Psychology | Education and Training | Administrative | Telecommunications</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Near Vision | Speech Recognition | Selective Attention | Written Comprehension | Information Ordering | Flexibility of Closure | Far Vision | Stamina | Written Expression | Trunk Strength | Dynamic Strength | Explosive Strength | Static Strength | Reaction Time | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Time Sharing | Perceptual Speed | Auditory Attention | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Dealing With Unpleasant, Angry, or Discourteous People | Contact With Others | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | E-Mail | Indoors, Environmentally Controlled | Time Pressure | Conflict Situations | Health and Safety of Other Workers | Dealing with Violent or Physically Aggressive People | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Freedom to Make Decisions | Deal With External Customers or the Public in General | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Disease or Infections | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Written Letters and Memos | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Consequence of Error | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Bailiffs | Child, Family, and School Social Workers | Coroners | Court, Municipal, and License Clerks | Criminal Justice and Law Enforcement Teachers, Postsecondary | Detectives and Criminal Investigators | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Medical and Health Services Managers | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Probation Officers and Correctional Treatment Specialists | Psychiatric Aides | Rehabilitation Counselors | Residential Advisors | Security Guards | Social and Community Service Managers | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Guard inmates in penal or rehabilitative institutions in accordance with established regulations and procedures. May guard prisoners in transit between jail, courtroom, prison, or other point. Includes deputy sheriffs and police who spend the majority of their time guarding prisoners in correctional institutions.</t>
+  </si>
+  <si>
+    <t>Arrange daily schedules for prisoners, including library visits, work assignments, family visits, and counseling appointments. | Assign duties to inmates, providing instructions as needed. | Conduct fire, safety, and sanitation inspections. | Conduct head counts to ensure that each prisoner is present. | Counsel inmates and respond to legitimate questions, concerns, and requests. | Drive passenger vehicles and trucks used to transport inmates to other institutions, courtrooms, hospitals, and work sites. | Guard facility entrances to screen visitors. | Inspect conditions of locks, window bars, grills, doors, and gates at correctional facilities to ensure security and help prevent escapes. | Inspect mail for the presence of contraband. | Investigate crimes that have occurred within an institution, or assist police in their investigations of crimes and inmates. | Issue clothing, tools, and other authorized items to inmates. | Maintain records of prisoners' identification and charges. | Monitor conduct of prisoners in housing unit, or during work or recreational activities, according to established policies, regulations, and procedures, to prevent escape or violence. | Participate in required job training. | Process or book convicted individuals into prison. | Provide to supervisors oral and written reports of the quality and quantity of work performed by inmates, inmate disturbances and rule violations, and unusual occurrences. | Record information, such as prisoner identification, charges, and incidents of inmate disturbance, keeping daily logs of prisoner activities. | Search for and recapture escapees. | Search prisoners and vehicles and conduct shakedowns of cells for valuables and contraband, such as weapons or drugs. | Serve meals, distribute commissary items, and dispense prescribed medication to prisoners. | Settle disputes between inmates. | Sponsor inmate recreational activities, such as newspapers and self-help groups. | Supervise and coordinate work of other correctional service officers. | Take fingerprints of arrestees, prisoners, or the general public. | Take prisoners into custody and escort to locations within and outside of facility, such as visiting room, courtroom, or airport. | Use nondisciplinary tools and equipment, such as a computer. | Use weapons, handcuffs, and physical force to maintain discipline and order among prisoners.</t>
+  </si>
+  <si>
+    <t>33-3021.00</t>
+  </si>
+  <si>
+    <t>Detectives and Criminal Investigators</t>
+  </si>
+  <si>
+    <t>Crime Scene Investigator (CSI) | Criminal Investigator | Detective | Fugitive Detective | Fugitive Investigator | Investigator | Narcotics Detective | Narcotics Investigator | Police Detective | Special Agent</t>
+  </si>
+  <si>
+    <t>AccessData FTK | Adobe Photoshop | Case management software | Computer aided composite drawing software | Corel WordPerfect Office Suite | Crime mapping software | DataWorks Plus Digital CrimeScene | DeChant Consulting Services iWitness | DesignWare 3D EyeWitness | Digital Image Management Solutions Crime Scene | ESRI ArcView | Email software | Eos Systems PhotoModeler | Geographic information system GIS software | Graphics software | Guidance Software EnCase Enterprise | Integrated Automated Fingerprint Identification System IAFIS | Law enforcement information databases | Linux | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Visio | Microsoft Word | National Crime Information Center (NCIC) database | National Integrated Ballistics Information Network NIBIN | SAS | SmartDraw Legal | Structured query language SQL | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension | Active Learning | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Law and Government | Public Safety and Security | English Language | Customer and Personal Service | Psychology | Computers and Electronics | Education and Training | Administrative | Administration and Management | Communications and Media | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Inductive Reasoning | Oral Expression | Problem Sensitivity | Deductive Reasoning | Written Comprehension | Near Vision | Speech Recognition | Speech Clarity | Information Ordering | Written Expression | Category Flexibility | Flexibility of Closure | Far Vision | Speed of Closure | Fluency of Ideas | Perceptual Speed | Selective Attention | Time Sharing | Originality</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | In an Enclosed Vehicle or Operate Enclosed Equipment | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Frequency of Decision Making | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Conflict Situations | Dealing With Unpleasant, Angry, or Discourteous People | Outdoors, Exposed to All Weather Conditions | Written Letters and Memos | Health and Safety of Other Workers | Importance of Repeating Same Tasks | Time Pressure | Physical Proximity | Indoors, Not Environmentally Controlled | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Administrative Law Judges, Adjudicators, and Hearing Officers | Bailiffs | Compliance Officers | Coroners | Correctional Officers and Jailers | Customs and Border Protection Officers | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Police and Detectives | Forensic Science Technicians | Fraud Examiners, Investigators and Analysts | Intelligence Analysts | Judicial Law Clerks | Lawyers | Police Identification and Records Officers | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Probation Officers and Correctional Treatment Specialists | Retail Loss Prevention Specialists | Security Guards | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Conduct investigations related to suspected violations of federal, state, or local laws to prevent or solve crimes.</t>
+  </si>
+  <si>
+    <t>Analyze completed police reports to determine what additional information and investigative work is needed. | Block or rope off scene and check perimeter to ensure that entire scene is secured. | Check victims for signs of life, such as breathing and pulse. | Collaborate with other offices and agencies to exchange information and coordinate activities. | Determine scope, timing, and direction of investigations. | Examine records and governmental agency files to find identifying data about suspects. | Examine records to locate links in chains of evidence or information. | Identify case issues and evidence needed, based on analysis of charges, complaints, or allegations of law violations. | Maintain surveillance of establishments to obtain identifying information on suspects. | Note, mark, and photograph location of objects found, such as footprints, tire tracks, bullets and bloodstains, and take measurements of the scene. | Notify command of situation and request assistance. | Notify, or request notification of, medical examiner or district attorney representative. | Obtain and verify evidence by interviewing and observing suspects and witnesses or by analyzing records. | Obtain facts or statements from complainants, witnesses, and accused persons and record interviews, using recording device. | Obtain summary of incident from officer in charge at crime scene, taking care to avoid disturbing evidence. | Organize scene search, assigning specific tasks and areas of search to individual officers and obtaining adequate lighting as necessary. | Participate or assist in raids and arrests. | Perform undercover assignments and maintain surveillance, including monitoring authorized wiretaps. | Prepare and serve search and arrest warrants. | Prepare charges or responses to charges, or information for court cases, according to formalized procedures. | Prepare reports that detail investigation findings. | Preserve, process, and analyze items of evidence obtained from crime scenes and suspects, placing them in proper containers and destroying evidence no longer needed. | Provide information to lab personnel concerning the source of an item of evidence and tests to be performed. | Question individuals or observe persons and establishments to confirm information given to patrol officers. | Record progress of investigation, maintain informational files on suspects, and submit reports to commanding officer or magistrate to authorize warrants. | Search for and collect evidence, such as fingerprints, using investigative equipment. | Secure deceased body and obtain evidence from it, preventing bystanders from tampering with it prior to medical examiner's arrival. | Secure persons at scene, keeping witnesses from conversing or leaving the scene before investigators arrive. | Summon medical help for injured individuals and alert medical personnel to take statements from them. | Testify before grand juries concerning criminal activity investigations.</t>
+  </si>
+  <si>
+    <t>33-3021.02</t>
+  </si>
+  <si>
+    <t>Police Identification and Records Officers</t>
+  </si>
+  <si>
+    <t>Crime Lab Analyst (Crime Laboratory Analyst) | Crime Scene Investigator (CSI) | Crime Scene Technician | Criminalist | Evidence Technician (Evidence Tech) | Field Identification Specialist | Forensic Specialist | Identification Technician (Identification Tech) | Latent Fingerprint Examiner | Police Officer</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Computer aided composite drawing software | DataWorks Plus Digital CrimeScene | Database software | DeChant Consulting Services iWitness | DesignWare 3D EyeWitness | Digital Image Management Solutions Crime Scene | Eos Systems PhotoModeler | Image enhancement software | Integrated Automated Fingerprint Identification System IAFIS | Linux | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | National Crime Information Center (NCIC) database | National Integrated Ballistics Information Network NIBIN | SmartDraw Legal | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Law and Government | Administrative | English Language | Public Safety and Security | Computers and Electronics | Customer and Personal Service | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Near Vision | Written Expression | Speech Recognition | Speech Clarity | Flexibility of Closure | Problem Sensitivity | Category Flexibility | Arm-Hand Steadiness | Fluency of Ideas | Selective Attention | Perceptual Speed | Visual Color Discrimination | Far Vision</t>
+  </si>
+  <si>
+    <t>E-Mail | Importance of Being Exact or Accurate | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Telephone Conversations | Determine Tasks, Priorities and Goals | In an Enclosed Vehicle or Operate Enclosed Equipment | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Contact With Others | Impact of Decisions on Co-workers or Company Results | Spend Time Sitting | Physical Proximity | Outdoors, Exposed to All Weather Conditions</t>
+  </si>
+  <si>
+    <t>Clinical Research Coordinators | Compliance Officers | Coroners | Detectives and Criminal Investigators | Digital Forensics Analysts | Environmental Compliance Inspectors | Environmental Science and Protection Technicians, Including Health | File Clerks | First-Line Supervisors of Police and Detectives | Forensic Science Technicians | Fraud Examiners, Investigators and Analysts | Government Property Inspectors and Investigators | Intelligence Analysts | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Paralegals and Legal Assistants | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Social Science Research Assistants | Statistical Assistants</t>
+  </si>
+  <si>
+    <t>Collect evidence at crime scene, classify and identify fingerprints, and photograph evidence for use in criminal and civil cases.</t>
+  </si>
+  <si>
+    <t>Analyze and process evidence at crime scenes, during autopsies, or in the laboratory, wearing protective equipment and using powders and chemicals. | Coordinate or conduct instructional classes or in-services, such as citizen police academy classes and crime scene training for other officers. | Create sketches and diagrams, by hand or computer software, to depict crime scenes. | Dust selected areas of crime scene and lift latent fingerprints, adhering to proper preservation procedures. | Identify, compare, classify, and file fingerprints, using systems such as Automated Fingerprint Identification System (AFIS) or the Henry Classification System. | Interview survivors, witnesses, suspects, and other law enforcement personnel. | Look for trace evidence, such as fingerprints, hairs, fibers, or shoe impressions, using alternative light sources when necessary. | Maintain records of evidence and write and review reports. | Package, store and retrieve evidence. | Perform emergency work during off-hours. | Photograph crime or accident scenes for evidence records. | Process film and prints from crime or accident scenes. | Serve as technical advisor and coordinate with other law enforcement workers or legal personnel to exchange information on crime scene collection activities. | Submit evidence to supervisors, crime labs, or court officials for legal proceedings. | Take fingerprints. | Testify in court and present evidence.</t>
+  </si>
+  <si>
+    <t>33-3021.06</t>
+  </si>
+  <si>
+    <t>Intelligence Analysts</t>
+  </si>
+  <si>
+    <t>Anti-Terrorist Analyst | Crime Analyst (Criminal Analyst) | Crime Intelligence Analyst (Criminal Intelligence Analyst) | Crime Research Specialist (Criminal Research Specialist) | Crime and Intelligence Analyst (Criminal and Intelligence Analyst) | Intel Analyst (Intelligence Analyst) | Intel Research Specialist (Intelligence Research Specialist) | Investigative Intel Analysts (Investigative Intelligence Analysts) | Police Crime and Intel Analyst (Police Crime and Intelligence Analyst) | Terrorism Research Specialist</t>
+  </si>
+  <si>
+    <t>Amazon Simple Storage Service S3 | Amazon Web Services AWS software | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Spark | Arrival Departure Information System ADIS | Automated Targeting System ATS | Bing | Biometric Storage System BSS | C++ | Chatbot software | Computer Linked Application Information Management System CLAIMS | Consular Consolidated Database CCD | Data visualization software | Django | ESRI ArcGIS software | ESRI ArcView | Email software | Encryption software | Enforcement Case Tracking System ENFORCE | Facebook | Firewall software | Flowcharting software | Geographic information system GIS software | Geographic information system GIS systems | Google | Google Cloud software | Google Earth Pro | Graphics creation software | Hypertext markup language HTML | IBM i2 Analyst's Notebook | JavaScript | LexisNexis | Link analysis software | LinkedIn | Linux | McAfee | Microsoft Access | Microsoft Azure software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Myspace | National Crime Information Center (NCIC) database | NortonLifeLock cybersecurity software | Oracle Business Intelligence Enterprise Edition | Oracle Java | Oracle PeopleSoft | Palantir Intelligence | Photo enhancement software | Python | R | Refugee, Asylum and Parole System RAPS | Relational database management software | SAP software | SAS | Snort | Splunk Enterprise | Statistical analysis software | Structured query language SQL | Student and Exchange Visitor Information System SEVIS | Tableau | Telephone analysis software | Telephone records software | TensorFlow | Teradata Database | Text mining software | Thomson Reuters CLEAR | Timeline software | Treasury Enforcement Communications System TECS | UNIX | Veritas NetBackup | Web browser software | Wireshark</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Speaking | Writing | Critical Thinking | Active Learning | Monitoring | Learning Strategies</t>
+  </si>
+  <si>
+    <t>English Language | Law and Government | Public Safety and Security | Computers and Electronics | Administrative | Communications and Media | Customer and Personal Service | Telecommunications</t>
+  </si>
+  <si>
+    <t>Inductive Reasoning | Oral Comprehension | Written Comprehension | Problem Sensitivity | Oral Expression | Written Expression | Deductive Reasoning | Information Ordering | Speech Recognition | Speech Clarity | Flexibility of Closure | Near Vision | Category Flexibility | Fluency of Ideas | Originality | Far Vision | Selective Attention | Perceptual Speed | Speed of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Indoors, Environmentally Controlled | Telephone Conversations | Spend Time Sitting | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure | Importance of Repeating Same Tasks | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Business Intelligence Analysts | Data Scientists | Detectives and Criminal Investigators | Digital Forensics Analysts | Financial Risk Specialists | Forensic Science Technicians | Fraud Examiners, Investigators and Analysts | Gambling Surveillance Officers and Gambling Investigators | Health Information Technologists and Medical Registrars | Information Security Analysts | Information Security Engineers | Management Analysts | Penetration Testers | Police Identification and Records Officers | Private Detectives and Investigators | Retail Loss Prevention Specialists | Security Management Specialists | Security Managers | Social Science Research Assistants | Statistical Assistants</t>
+  </si>
+  <si>
+    <t>Gather, analyze, or evaluate information from a variety of sources, such as law enforcement databases, surveillance, intelligence networks or geographic information systems. Use intelligence data to anticipate and prevent organized crime activities, such as terrorism.</t>
+  </si>
+  <si>
+    <t>Analyze intelligence data to identify patterns and trends in criminal activity. | Collaborate with representatives from other government and intelligence organizations to share information or coordinate intelligence activities. | Conduct presentations of analytic findings. | Design, use, or maintain databases and software applications, such as geographic information systems (GIS) mapping and artificial intelligence tools. | Develop defense plans or tactics, using intelligence and other information. | Establish criminal profiles to aid in connecting criminal organizations with their members. | Evaluate records of communications, such as telephone calls, to plot activity and determine the size and location of criminal groups and members. | Gather and evaluate information, using tools such as aerial photographs, radar equipment, or sensitive radio equipment. | Gather intelligence information by field observation, confidential information sources, or public records. | Gather, analyze, correlate, or evaluate information from a variety of resources, such as law enforcement databases. | Identify gaps in information. | Interview, interrogate, or interact with witnesses or crime suspects to collect human intelligence. | Link or chart suspects to criminal organizations or events to determine activities and interrelationships. | Operate cameras, radios, or other surveillance equipment to intercept communications or document activities. | Predict future gang, organized crime, or terrorist activity, using analyses of intelligence data. | Prepare comprehensive written reports, presentations, maps, or charts, based on research, collection, and analysis of intelligence data. | Prepare plans to intercept foreign communications transmissions. | Study activities relating to narcotics, money laundering, gangs, auto theft rings, terrorism, or other national security threats. | Study communication code languages or foreign languages to translate intelligence. | Study the assets of criminal suspects to determine the flow of money from or to targeted groups. | Validate known intelligence with data from other sources.</t>
+  </si>
+  <si>
+    <t>33-3031.00</t>
+  </si>
+  <si>
+    <t>Fish and Game Wardens</t>
+  </si>
+  <si>
+    <t>Fisheries Enforcement Officer | Game Warden | Natural Resource Officer | State Game Warden | State Wildlife Officer | Wildlife Conservation Officer | Wildlife Officer</t>
+  </si>
+  <si>
+    <t>Database software | Global positioning system GPS software | Mapping software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Puppet | Swift | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Reading Comprehension | Monitoring | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>Law and Government | Public Safety and Security | Biology | English Language | Customer and Personal Service | Psychology | Geography | Sociology and Anthropology | Education and Training | Administration and Management | Administrative | Computers and Electronics | Communications and Media</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Inductive Reasoning | Problem Sensitivity | Speech Clarity | Speech Recognition | Deductive Reasoning | Near Vision | Far Vision | Written Comprehension | Written Expression | Flexibility of Closure | Spatial Orientation | Category Flexibility | Information Ordering | Speed of Closure | Depth Perception | Stamina | Multilimb Coordination | Control Precision | Time Sharing | Selective Attention</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Telephone Conversations | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General | E-Mail | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Time Pressure | Exposed to Very Hot or Cold Temperatures | Dealing With Unpleasant, Angry, or Discourteous People | Level of Competition | Exposed to Minor Burns, Cuts, Bites, or Stings | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Animal Control Workers | Biologists | Conservation Scientists | Environmental Compliance Inspectors | Environmental Restoration Planners | Environmental Scientists and Specialists, Including Health | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Firefighting and Prevention Workers | Fishing and Hunting Workers | Forest Fire Inspectors and Prevention Specialists | Forest and Conservation Technicians | Forest and Conservation Workers | Foresters | Forestry and Conservation Science Teachers, Postsecondary | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Park Naturalists | Police and Sheriff's Patrol Officers | Range Managers | Transit and Railroad Police | Zoologists and Wildlife Biologists</t>
+  </si>
+  <si>
+    <t>Patrol assigned area to prevent fish and game law violations. Investigate reports of damage to crops or property by wildlife. Compile biological data.</t>
+  </si>
+  <si>
+    <t>Address schools, civic groups, sporting clubs, or the media to disseminate information concerning wildlife conservation and regulations. | Arrange for disposition of fish or game illegally taken or possessed. | Collect and report information on populations or conditions of fish and wildlife in their habitats, availability of game food or cover, or suspected pollution. | Compile and present evidence for court actions. | Design or implement control measures to prevent or counteract damage caused by wildlife or people. | Document the extent of crop, property, or habitat damage and make financial loss estimates or compensation recommendations. | Inspect commercial operations relating to fish or wildlife, recreation, or protected areas. | Investigate crop, property, or habitat damage or destruction or instances of water pollution to determine causes and to advise property owners of preventive measures. | Investigate hunting accidents or reports of fish or game law violations. | Issue licenses, permits, or other documentation. | Issue warnings or citations and file reports as necessary. | Participate in firefighting efforts. | Participate in search-and-rescue operations. | Patrol assigned areas by car, boat, airplane, horse, or on foot to enforce game, fish, or boating laws or to manage wildlife programs, lakes, or land. | Perform facilities maintenance work, such as constructing or repairing structures or controlling weeds or pests. | Promote or provide hunter or trapper safety training. | Protect and preserve native wildlife, plants, or ecosystems. | Provide advice or information to park or reserve visitors. | Provide assistance to other local law enforcement agencies as required. | Recommend revisions in hunting and trapping regulations or in animal management programs so that wildlife balances or habitats can be maintained. | Seize equipment used in fish and game law violations. | Serve warrants and make arrests. | Supervise the activities of seasonal workers. | Survey areas and compile figures of bag counts of hunters to determine the effectiveness of control measures.</t>
+  </si>
+  <si>
+    <t>33-3041.00</t>
+  </si>
+  <si>
+    <t>Parking Enforcement Workers</t>
+  </si>
+  <si>
+    <t>Parking Control Officer | Parking Enforcement Officer (PEO) | Parking Enforcement Technician | Parking Enforcer | Parking Officer | Parking Regulation Enforcement Officer | Parking Technician | Ticket Writer</t>
+  </si>
+  <si>
+    <t>Complus Data Innovations FastTrack | Integrated Parking Solutions MApp | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Ticket issuing software | Vehicle information databases | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>English Language | Public Safety and Security | Law and Government | Computers and Electronics | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Expression | Speech Clarity | Information Ordering | Oral Comprehension | Near Vision | Speech Recognition | Far Vision | Problem Sensitivity | Written Expression | Perceptual Speed | Selective Attention | Inductive Reasoning | Deductive Reasoning | Written Comprehension | Control Precision</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Enclosed Vehicle or Operate Enclosed Equipment | Dealing With Unpleasant, Angry, or Discourteous People | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Contact With Others | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialists | Compliance Officers | Crossing Guards and Flaggers | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Security Workers | Highway Maintenance Workers | Light Truck Drivers | Parking Attendants | Passenger Attendants | Police and Sheriff's Patrol Officers | Railroad Conductors and Yardmasters | Security Guards | Shuttle Drivers and Chauffeurs | Subway and Streetcar Operators | Taxi Drivers | Traffic Technicians | Transit and Railroad Police | Transportation Security Screeners | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Patrol assigned area, such as public parking lot or city streets to issue tickets to overtime parking violators and illegally parked vehicles.</t>
+  </si>
+  <si>
+    <t>Appear in court at hearings regarding contested traffic citations. | Assign and review the work of subordinates. | Collect coins deposited in meters. | Enter and retrieve information pertaining to vehicle registration, identification, and status, using hand-held computers. | Identify vehicles in violation of parking codes, checking with dispatchers when necessary to confirm identities or to determine whether vehicles need to be booted or towed. | Investigate and answer complaints regarding contested parking citations, determining their validity and routing them appropriately. | Locate lost, stolen, and counterfeit parking permits, and take necessary enforcement action. | Maintain assigned equipment and supplies, such as hand-held citation computers, citation books, rain gear, tire-marking chalk, and street cones. | Maintain close communications with dispatching personnel, using two-way radios or cell phones. | Make arrangements for illegally parked or abandoned vehicles to be towed, and direct tow-truck drivers to the correct vehicles. | Mark tires of parked vehicles with chalk and record time of marking, and return at regular intervals to ensure that parking time limits are not exceeded. | Observe and report hazardous conditions, such as missing traffic signals or signs, and street markings that need to be repainted. | Patrol an assigned area by vehicle or on foot to ensure public compliance with existing parking ordinance. | Perform simple vehicle maintenance procedures, such as checking oil and gas, and report mechanical problems to supervisors. | Perform traffic control duties such as setting up barricades and temporary signs, placing bags on parking meters to limit their use, or directing traffic. | Prepare and maintain required records, including logs of parking enforcement activities, and records of contested citations. | Provide assistance to motorists needing help with problems, such as flat tires, keys locked in cars, or dead batteries. | Provide information to the public regarding parking regulations and facilities, and the location of streets, buildings and points of interest. | Respond to and make radio dispatch calls regarding parking violations and complaints. | Train new or temporary staff. | Wind parking meter clocks. | Write warnings and citations for illegally parked vehicles.</t>
+  </si>
+  <si>
+    <t>33-3051.00</t>
+  </si>
+  <si>
+    <t>Police and Sheriff's Patrol Officers</t>
+  </si>
+  <si>
+    <t>Deputy | Deputy Sheriff | Law Enforcement Officer | Patrol Deputy | Patrol Officer | Peace Officer | Police Officer | Police Patrol Officer | Public Safety Officer | State Trooper</t>
+  </si>
+  <si>
+    <t>Computer aided composite drawing software | Computer aided dispatch software | Corel WordPerfect Office Suite | Crime mapping software | Database software | DesignWare 3D EyeWitness | ESRI ArcView | Email software | IBM Lotus 1-2-3 | Integrated Automated Fingerprint Identification System IAFIS | Law enforcement information databases | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | National Crime Information Center (NCIC) database | National Integrated Ballistics Information Network NIBIN | SmartDraw Legal | SmugMug Flickr | Spillman Technologies Records Management | The CAD Zone The Crime Zone | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Active Learning | Reading Comprehension | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | English Language | Psychology | Customer and Personal Service | Education and Training | Telecommunications | Administration and Management | Administrative | Computers and Electronics | Communications and Media | Transportation | Geography | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Inductive Reasoning | Deductive Reasoning | Oral Expression | Written Comprehension | Speech Clarity | Information Ordering | Near Vision | Far Vision | Speech Recognition | Flexibility of Closure | Written Expression | Trunk Strength | Category Flexibility | Selective Attention | Speed of Closure | Multilimb Coordination | Static Strength | Explosive Strength | Dynamic Strength | Reaction Time | Response Orientation | Perceptual Speed | Arm-Hand Steadiness | Time Sharing | Memorization | Originality | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Being Exact or Accurate | In an Enclosed Vehicle or Operate Enclosed Equipment | Telephone Conversations | Frequency of Decision Making | Dealing With Unpleasant, Angry, or Discourteous People | Work With or Contribute to a Work Group or Team | Outdoors, Exposed to All Weather Conditions | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Health and Safety of Other Workers | Conflict Situations | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Exposed to Extremely Bright or Inadequate Lighting Conditions | Physical Proximity | Dealing with Violent or Physically Aggressive People | Written Letters and Memos | Time Pressure | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment | Importance of Repeating Same Tasks | Consequence of Error | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets</t>
+  </si>
+  <si>
+    <t>Administrative Law Judges, Adjudicators, and Hearing Officers | Bailiffs | Compliance Officers | Coroners | Correctional Officers and Jailers | Court, Municipal, and License Clerks | Customs and Border Protection Officers | Detectives and Criminal Investigators | First-Line Supervisors of Correctional Officers | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Intelligence Analysts | Judges, Magistrate Judges, and Magistrates | Police Identification and Records Officers | Private Detectives and Investigators | Probation Officers and Correctional Treatment Specialists | Public Safety Telecommunicators | Security Guards | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Maintain order and protect life and property by enforcing local, tribal, state, or federal laws and ordinances. Perform a combination of the following duties: patrol a specific area; direct traffic; issue traffic summonses; investigate accidents; apprehend and arrest suspects, or serve legal processes of courts. Includes police officers working at educational institutions.</t>
+  </si>
+  <si>
+    <t>Conduct community programs for all ages concerning topics such as drugs and violence. | Direct traffic flow and reroute traffic in case of emergencies. | Drive vehicles or patrol specific areas to detect law violators, issue citations, and make arrests. | Evaluate complaint and emergency-request information to determine response requirements. | Execute arrest warrants, locating and taking persons into custody. | Identify, pursue, and arrest suspects and perpetrators of criminal acts. | Inform citizens of community services and recommend options to facilitate longer-term problem resolution. | Investigate illegal or suspicious activities. | Investigate traffic accidents and other accidents to determine causes and to determine if a crime has been committed. | Locate and confiscate real or personal property, as directed by court order. | Monitor traffic to ensure motorists observe traffic regulations and exhibit safe driving procedures. | Monitor, note, report, and investigate suspicious persons and situations, safety hazards, and unusual or illegal activity in patrol area. | Notify patrol units to take violators into custody or to provide needed assistance or medical aid. | Patrol and guard courthouses, grand jury rooms, or assigned areas to provide security, enforce laws, maintain order, and arrest violators. | Patrol specific area on foot, horseback, or motorized conveyance, responding promptly to calls for assistance. | Photograph or draw diagrams of crime or accident scenes and interview principals and eyewitnesses. | Place people in protective custody. | Process prisoners, and prepare and maintain records of prisoner bookings and prisoner status during booking and pre-trial process. | Provide for public safety by maintaining order, responding to emergencies, protecting people and property, enforcing motor vehicle and criminal laws, and promoting good community relations. | Provide road information to assist motorists. | Question individuals entering secured areas to determine their business, directing and rerouting individuals as necessary. | Record facts to prepare reports that document incidents and activities. | Relay complaint and emergency-request information to appropriate agency dispatchers. | Render aid to accident survivors and other persons requiring first aid for physical injuries. | Review facts of incidents to determine if criminal act or statute violations were involved. | Serve statements of claims, subpoenas, summonses, jury summonses, orders to pay alimony, and other court orders. | Supervise law enforcement staff, such as jail staff, officers, and deputy sheriffs. | Testify in court to present evidence or act as witness in traffic and criminal cases. | Transport or escort prisoners and defendants en route to courtrooms, prisons or jails, attorneys' offices, or medical facilities. | Verify that the proper legal charges have been made against law offenders.</t>
+  </si>
+  <si>
+    <t>33-3051.04</t>
+  </si>
+  <si>
+    <t>Customs and Border Protection Officers</t>
+  </si>
+  <si>
+    <t>Canine Enforcement Officer (K-9 Enforcement Officer) | Customs Inspector | Customs Officer | Import Specialist | Special Agent | US Customs and Border Protection Officer (US CBPO)</t>
+  </si>
+  <si>
+    <t>Automated Manifest System AMS | Corel WordPerfect Office Suite | Global positioning system GPS software | IBM WebSphere MQ | Law enforcement information databases | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | National Crime Information Center (NCIC) database | SAP software | Treasury Enforcement Communications System TECS</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension | Monitoring | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>Law and Government | Public Safety and Security | English Language | Customer and Personal Service | Psychology | Administrative | Computers and Electronics | Geography | Sociology and Anthropology | Education and Training | Foreign Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Inductive Reasoning | Near Vision | Written Comprehension | Deductive Reasoning | Speech Clarity | Speech Recognition | Written Expression | Flexibility of Closure | Information Ordering | Perceptual Speed | Selective Attention | Far Vision | Time Sharing</t>
+  </si>
+  <si>
+    <t>E-Mail | Contact With Others | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Telephone Conversations | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Freedom to Make Decisions | Physical Proximity | Importance of Repeating Same Tasks | Exposed to Contaminants | Outdoors, Exposed to All Weather Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Time Pressure | Conflict Situations | Exposed to Extremely Bright or Inadequate Lighting Conditions | Exposed to Very Hot or Cold Temperatures | Written Letters and Memos | Exposed to Hazardous Equipment | Spend Time Making Repetitive Motions | Level of Competition | Health and Safety of Other Workers | Exposed to Disease or Infections</t>
+  </si>
+  <si>
+    <t>Agricultural Inspectors | Cargo and Freight Agents | Compliance Managers | Compliance Officers | Customs Brokers | Detectives and Criminal Investigators | Environmental Compliance Inspectors | First-Line Supervisors of Police and Detectives | Fraud Examiners, Investigators and Analysts | Freight Forwarders | Government Property Inspectors and Investigators | Intelligence Analysts | Police Identification and Records Officers | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Security Guards | Tax Examiners and Collectors, and Revenue Agents | Transit and Railroad Police | Transportation Inspectors | Transportation Security Screeners</t>
+  </si>
+  <si>
+    <t>Investigate and inspect persons, common carriers, goods, and merchandise, arriving in or departing from the United States or between states to detect violations of immigration and customs laws and regulations.</t>
+  </si>
+  <si>
+    <t>Collect samples of merchandise for examination, appraisal, or testing. | Detain persons found to be in violation of customs or immigration laws and arrange for legal action, such as deportation. | Determine duty and taxes to be paid on goods. | Examine immigration applications, visas, and passports and interview persons to determine eligibility for admission, residence, and travel in the U.S. | Inspect cargo, baggage, and personal articles entering or leaving U.S. for compliance with revenue laws and U.S. customs regulations. | Institute civil and criminal prosecutions and cooperate with other law enforcement agencies in the investigation and prosecution of those in violation of immigration or customs laws. | Interpret and explain laws and regulations to travelers, prospective immigrants, shippers, and manufacturers. | Investigate applications for duty refunds and petition for remission or mitigation of penalties when warranted. | Locate and seize contraband, undeclared merchandise, and vehicles, aircraft, or boats that contain such merchandise. | Record and report job-related activities, findings, transactions, violations, discrepancies, and decisions. | Testify regarding decisions at immigration appeals or in federal court.</t>
+  </si>
+  <si>
+    <t>33-3052.00</t>
+  </si>
+  <si>
+    <t>Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Law Enforcement Officer | Patrol Man | Patrol Officer | Patrolman | Police Captain | Police Specialist | Railroad Police | Railroad Police Officer | Transit Police Officer</t>
+  </si>
+  <si>
+    <t>Crime mapping software | Integrated Automated Fingerprint Identification System IAFIS | Law enforcement information databases | MapInfo Professional | MapInfo StreetPro | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | National Crime Information Center (NCIC) database | SmugMug Flickr | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Monitoring | Active Learning | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | English Language | Customer and Personal Service | Transportation | Education and Training | Geography | Psychology | Computers and Electronics | Administration and Management | Telecommunications | Communications and Media</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Oral Expression | Inductive Reasoning | Speech Clarity | Written Expression | Deductive Reasoning | Near Vision | Far Vision | Speech Recognition | Flexibility of Closure | Information Ordering | Written Comprehension | Selective Attention | Auditory Attention | Trunk Strength | Speed of Closure | Perceptual Speed | Category Flexibility | Originality | Fluency of Ideas | Stamina | Explosive Strength | Static Strength | Response Orientation | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Time Sharing | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>E-Mail | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General | Contact With Others | Health and Safety of Other Workers | Telephone Conversations | Frequency of Decision Making | Freedom to Make Decisions | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Conflict Situations | Determine Tasks, Priorities and Goals | Physical Proximity | Indoors, Not Environmentally Controlled | Dealing With Unpleasant, Angry, or Discourteous People | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Written Letters and Memos | Time Pressure | Exposed to Hazardous Conditions | Consequence of Error | Dealing with Violent or Physically Aggressive People | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialists | Compliance Officers | Correctional Officers and Jailers | Crossing Guards and Flaggers | Customs and Border Protection Officers | Detectives and Criminal Investigators | Dispatchers, Except Police, Fire, and Ambulance | Fire Inspectors and Investigators | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Locomotive Engineers | Parking Enforcement Workers | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Public Safety Telecommunicators | Railroad Conductors and Yardmasters | Security Guards | Subway and Streetcar Operators | Transportation Security Screeners</t>
+  </si>
+  <si>
+    <t>Protect and police railroad and transit property, employees, or passengers.</t>
+  </si>
+  <si>
+    <t>Apprehend or remove trespassers or thieves from railroad property or coordinate with law enforcement agencies in apprehensions and removals. | Direct or coordinate the daily activities or training of security staff. | Direct security activities at derailments, fires, floods, or strikes involving railroad property. | Enforce traffic laws regarding the transit system and reprimand individuals who violate them. | Examine credentials of unauthorized persons attempting to enter secured areas. | Interview neighbors, associates, or former employers of job applicants to verify personal references or to obtain work history data. | Investigate or direct investigations of freight theft, suspicious damage or loss of passengers' valuables, or other crimes on railroad property. | Monitor transit areas and conduct security checks to protect railroad properties, patrons, and employees. | Patrol railroad yards, cars, stations, or other facilities to protect company property or shipments and to maintain order. | Plan or implement special safety or preventive programs, such as fire or accident prevention. | Prepare reports documenting investigation activities and results. | Provide training to the public or law enforcement personnel in railroad safety or security.</t>
+  </si>
+  <si>
+    <t>33-9011.00</t>
+  </si>
+  <si>
+    <t>Animal Control Workers</t>
+  </si>
+  <si>
+    <t>ACO (Animal Control Officer) | Animal Attendant | Animal Cruelty Investigator | Animal Enforcement Officer | Animal Instructor Officer | Animal Ordinance Enforcement Officer | Animal Park Code Enforcement Officer | Animal Safety Officer | Animal Services Officer | Community Service Officer</t>
+  </si>
+  <si>
+    <t>ARK Software Ark Shelter Software | Animal Shelter Manager | CISCO Software ACS Animal Control System | Esri ArcGIS | Geographic information system GIS software | Geographic information system GIS systems | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Multiple Options Animal Shelter Management System | RescueConnection Software ShelterConntection | RoseRush Services Shelter Pro | SAP software | TRAX Animal Control and Dog Warden Officer Software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Monitoring | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | English Language | Customer and Personal Service | Administrative | Education and Training | Biology | Telecommunications | Communications and Media | Transportation | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Problem Sensitivity | Oral Comprehension | Deductive Reasoning | Speech Clarity | Inductive Reasoning | Written Comprehension | Speech Recognition | Far Vision | Near Vision | Static Strength | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Category Flexibility | Information Ordering | Written Expression</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General | Dealing With Unpleasant, Angry, or Discourteous People | Contact With Others | Frequency of Decision Making | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Freedom to Make Decisions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Disease or Infections | Written Letters and Memos | Conflict Situations | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Exposed to Minor Burns, Cuts, Bites, or Stings | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Consequence of Error | Indoors, Environmentally Controlled | Time Pressure | Exposed to Extremely Bright or Inadequate Lighting Conditions | Physical Proximity | Outdoors, Under Cover | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers | Importance of Repeating Same Tasks | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Agricultural Inspectors | Animal Breeders | Animal Caretakers | Animal Scientists | Animal Trainers | Coroners | Correctional Officers and Jailers | Detectives and Criminal Investigators | Environmental Compliance Inspectors | Farmworkers, Farm, Ranch, and Aquacultural Animals | Fish and Game Wardens | Police Identification and Records Officers | Police and Sheriff's Patrol Officers | Private Detectives and Investigators | Security Guards | Transit and Railroad Police | Veterinarians | Veterinary Assistants and Laboratory Animal Caretakers | Veterinary Technologists and Technicians | Zoologists and Wildlife Biologists</t>
+  </si>
+  <si>
+    <t>Handle animals for the purpose of investigations of mistreatment, or control of abandoned, dangerous, or unattended animals.</t>
+  </si>
+  <si>
+    <t>Answer inquiries from the public concerning animal control operations. | Capture and remove stray, uncontrolled, or abused animals from undesirable conditions, using nets, nooses, or tranquilizer darts as necessary. | Clean facilities and equipment such as dog pens and animal control trucks. | Contact animal owners to inform them that their pets are at animal holding facilities. | Educate the public about animal welfare, and animal control laws and regulations. | Euthanize rabid, unclaimed, or severely injured animals. | Examine animal licenses, and inspect establishments housing animals for compliance with laws. | Examine animals for injuries or malnutrition, and arrange for any necessary medical treatment. | Investigate reports of animal attacks or animal cruelty, interviewing witnesses, collecting evidence, and writing reports. | Issue warnings or citations in connection with animal-related offenses, or contact police to report violations and request arrests. | Organize the adoption of unclaimed animals. | Prepare for prosecutions related to animal treatment, and give evidence in court. | Remove captured animals from animal-control service vehicles and place animals in shelter cages or other enclosures. | Supply animals with food, water, and personal care. | Train police officers in dog handling and training techniques for tracking, crowd control, and narcotics and bomb detection. | Write reports of activities, and maintain files of impoundments and dispositions of animals.</t>
+  </si>
+  <si>
+    <t>33-9021.00</t>
+  </si>
+  <si>
+    <t>Private Detectives and Investigators</t>
+  </si>
+  <si>
+    <t>Asset Protection Detective | Field Investigator | Investigator | Loss Prevention Agent | Loss Prevention Associate | Loss Prevention Detective | Loss Prevention Investigator | Loss Prevention Officer | Private Investigator | Special Investigator</t>
+  </si>
+  <si>
+    <t>Computer imaging software | Email software | Facebook | LexisNexis | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Writing | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Law and Government | Computers and Electronics | Administrative | Administration and Management | Public Safety and Security | Psychology</t>
+  </si>
+  <si>
+    <t>Inductive Reasoning | Oral Comprehension | Oral Expression | Problem Sensitivity | Near Vision | Written Comprehension | Written Expression | Deductive Reasoning | Speech Recognition | Speech Clarity | Information Ordering | Selective Attention | Flexibility of Closure | Far Vision | Category Flexibility | Fluency of Ideas | Perceptual Speed | Originality</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Importance of Being Exact or Accurate | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Contact With Others | Time Pressure | Spend Time Sitting | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Written Letters and Memos | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Claims Adjusters, Examiners, and Investigators | Compliance Officers | Coroners | Credit Authorizers, Checkers, and Clerks | Detectives and Criminal Investigators | Eligibility Interviewers, Government Programs | Financial Examiners | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Forensic Science Technicians | Fraud Examiners, Investigators and Analysts | Government Property Inspectors and Investigators | Intelligence Analysts | Lawyers | Legal Secretaries and Administrative Assistants | Management Analysts | Paralegals and Legal Assistants | Police Identification and Records Officers | Police and Sheriff's Patrol Officers | Retail Loss Prevention Specialists</t>
+  </si>
+  <si>
+    <t>Gather, analyze, compile, and report information regarding individuals or organizations to clients, or detect occurrences of unlawful acts or infractions of rules in private establishment.</t>
+  </si>
+  <si>
+    <t>Alert appropriate personnel to suspects' locations. | Conduct personal background investigations, such as pre-employment checks, to obtain information about an individual's character, financial status, or personal history. | Conduct private investigations on a paid basis. | Confer with establishment officials, security departments, police, or postal officials to identify problems, provide information, or receive instructions. | Count cash and review transactions, sales checks, or register tapes to verify amounts or to identify shortages. | Expose fraudulent insurance claims or stolen funds. | Investigate companies' financial standings, or locate funds stolen by embezzlers, using accounting skills. | Observe and document activities of individuals to detect unlawful acts or to obtain evidence for cases, using binoculars and still or video cameras. | Obtain and analyze information on suspects, crimes, or disturbances to solve cases, to identify criminal activity, or to gather information for court cases. | Perform undercover operations, such as evaluating the performance or honesty of employees by posing as customers or employees. | Question persons to obtain evidence for cases of divorce, child custody, or missing persons or information about individuals' character or financial status. | Search computer databases, credit reports, public records, tax or legal filings, or other resources to locate persons or to compile information for investigations. | Testify at hearings or court trials to present evidence. | Write reports or case summaries to document investigations.</t>
+  </si>
+  <si>
+    <t>33-9031.00</t>
+  </si>
+  <si>
+    <t>Gambling Surveillance Officers and Gambling Investigators</t>
+  </si>
+  <si>
+    <t>Casino Enforcement Agent | Gaming Investigator | Security Officer | Surveillance Agent | Surveillance Investigator | Surveillance Monitor | Surveillance Observer | Surveillance Officer | Surveillance Operator | Surveillance Technician</t>
+  </si>
+  <si>
+    <t>FileMaker Pro | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Paint | Microsoft PowerPoint | Microsoft Word | iView Systems</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening | Reading Comprehension | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>English Language | Public Safety and Security | Computers and Electronics | Mathematics | Administrative | Education and Training | Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Selective Attention | Far Vision | Oral Comprehension | Near Vision | Written Expression | Inductive Reasoning | Oral Expression | Flexibility of Closure | Deductive Reasoning | Perceptual Speed | Speech Recognition | Speech Clarity | Speed of Closure | Information Ordering | Written Comprehension | Time Sharing</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Telephone Conversations | Importance of Being Exact or Accurate | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Physical Proximity | Determine Tasks, Priorities and Goals | Conflict Situations | Coordinate or Lead Others in Accomplishing Work Activities | Written Letters and Memos | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Camera Operators, Television, Video, and Film | Compliance Managers | Computer Network Support Specialists | Construction and Building Inspectors | Detectives and Criminal Investigators | Digital Forensics Analysts | First-Line Supervisors of Gambling Services Workers | First-Line Supervisors of Security Workers | Fraud Examiners, Investigators and Analysts | Gambling Managers | Information Security Analysts | Information Security Engineers | Intelligence Analysts | Management Analysts | Penetration Testers | Private Detectives and Investigators | Retail Loss Prevention Specialists | Security Management Specialists | Security Managers | Telecommunications Equipment Installers and Repairers, Except Line Installers</t>
+  </si>
+  <si>
+    <t>Observe gambling operation for irregular activities such as cheating or theft by either employees or patrons. Investigate potential threats to gambling assets such as money, chips, and gambling equipment. Act as oversight and security agent for management and customers.</t>
+  </si>
+  <si>
+    <t>Act as oversight or security agents for management or customers. | Develop and maintain log of surveillance observations. | Inspect and monitor audio or video surveillance equipment to ensure it is working appropriately. | Monitor establishment activities to ensure adherence to all state gaming regulations and company policies and procedures. | Observe casino or casino hotel operations for irregular activities, such as cheating or theft by employees or patrons, using audio and video equipment and one-way mirrors. | Report all violations and suspicious behaviors to supervisors, verbally or in writing. | Review video surveillance footage. | Supervise or train surveillance observers.</t>
+  </si>
+  <si>
+    <t>33-9032.00</t>
+  </si>
+  <si>
+    <t>Security Guards</t>
+  </si>
+  <si>
+    <t>Armed Security Officer | Campus Security Officer (CSO) | Custom Protection Officer (CPO) | Customer Service Security Officer | Hotel Security Officer | Loss Prevention Officer | Safety and Security Officer | Security Agent | Security Guard | Security Officer</t>
+  </si>
+  <si>
+    <t>Corel WordPerfect Office Suite | FaceTime | IBM Lotus 1-2-3 | McAfee | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft SharePoint | Microsoft Word | NortonLifeLock cybersecurity software | Wireshark</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | English Language | Computers and Electronics | Administration and Management | Education and Training | Telecommunications | Administrative | Law and Government | Therapy and Counseling | Psychology | Medicine and Dentistry</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Far Vision | Oral Comprehension | Speech Recognition | Near Vision | Selective Attention | Oral Expression | Speech Clarity | Deductive Reasoning | Flexibility of Closure | Information Ordering | Inductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Health and Safety of Other Workers | Deal With External Customers or the Public in General | Contact With Others | Telephone Conversations | Freedom to Make Decisions | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | E-Mail | Work With or Contribute to a Work Group or Team | Conflict Situations | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialists | Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Correctional Officers and Jailers | Crossing Guards and Flaggers | Dispatchers, Except Police, Fire, and Ambulance | Fire Inspectors and Investigators | Firefighters | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Security Workers | Forest Fire Inspectors and Prevention Specialists | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Parking Enforcement Workers | Police and Sheriff's Patrol Officers | Public Safety Telecommunicators | Retail Loss Prevention Specialists | Security Management Specialists | Security Managers | Transit and Railroad Police | Transportation Security Screeners | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Guard, patrol, or monitor premises to prevent theft, violence, or infractions of rules. May operate x-ray and metal detector equipment.</t>
+  </si>
+  <si>
+    <t>Answer alarms and investigate disturbances. | Answer telephone calls to take messages, answer questions, and provide information during non-business hours or when switchboard is closed. | Call police or fire departments in cases of emergency, such as fire or presence of unauthorized persons. | Circulate among visitors, patrons, or employees to preserve order and protect property. | Escort or drive motor vehicle to transport individuals to specified locations or to provide personal protection. | Inspect and adjust security systems, equipment, or machinery to ensure operational use and to detect evidence of tampering. | Lock doors and gates of entrances and exits to secure buildings. | Monitor and adjust controls that regulate building systems, such as air conditioning, furnace, or boiler. | Monitor and authorize entrance and departure of employees, visitors, and other persons to guard against theft and maintain security of premises. | Operate detecting devices to screen individuals and prevent passage of prohibited articles into restricted areas. | Patrol industrial or commercial premises to prevent and detect signs of intrusion and ensure security of doors, windows, and gates. | Respond to medical emergencies by administering basic first aid or by obtaining assistance from paramedics. | Warn persons of rule infractions or violations, and apprehend or evict violators from premises, using force when necessary. | Write reports of daily activities and irregularities, such as equipment or property damage, theft, presence of unauthorized persons, or unusual occurrences.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1979,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" t="s">
+        <v>152</v>
+      </c>
+      <c r="K14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" t="s">
+        <v>161</v>
+      </c>
+      <c r="I15" t="s">
+        <v>162</v>
+      </c>
+      <c r="J15" t="s">
+        <v>163</v>
+      </c>
+      <c r="K15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" t="s">
+        <v>172</v>
+      </c>
+      <c r="I16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J16" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" t="s">
+        <v>181</v>
+      </c>
+      <c r="G17" t="s">
+        <v>182</v>
+      </c>
+      <c r="H17" t="s">
+        <v>183</v>
+      </c>
+      <c r="I17" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" t="s">
+        <v>205</v>
+      </c>
+      <c r="J19" t="s">
+        <v>206</v>
+      </c>
+      <c r="K19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F20" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H20" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" t="s">
+        <v>216</v>
+      </c>
+      <c r="J20" t="s">
+        <v>217</v>
+      </c>
+      <c r="K20" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F21" t="s">
+        <v>224</v>
+      </c>
+      <c r="G21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H21" t="s">
+        <v>226</v>
+      </c>
+      <c r="I21" t="s">
+        <v>227</v>
+      </c>
+      <c r="J21" t="s">
+        <v>228</v>
+      </c>
+      <c r="K21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" t="s">
+        <v>236</v>
+      </c>
+      <c r="H22" t="s">
+        <v>237</v>
+      </c>
+      <c r="I22" t="s">
+        <v>238</v>
+      </c>
+      <c r="J22" t="s">
+        <v>239</v>
+      </c>
+      <c r="K22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B23" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" t="s">
+        <v>245</v>
+      </c>
+      <c r="F23" t="s">
+        <v>246</v>
+      </c>
+      <c r="G23" t="s">
+        <v>247</v>
+      </c>
+      <c r="H23" t="s">
+        <v>248</v>
+      </c>
+      <c r="I23" t="s">
+        <v>249</v>
+      </c>
+      <c r="J23" t="s">
+        <v>250</v>
+      </c>
+      <c r="K23" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" t="s">
+        <v>256</v>
+      </c>
+      <c r="F24" t="s">
+        <v>257</v>
+      </c>
+      <c r="G24" t="s">
+        <v>258</v>
+      </c>
+      <c r="H24" t="s">
+        <v>259</v>
+      </c>
+      <c r="I24" t="s">
+        <v>260</v>
+      </c>
+      <c r="J24" t="s">
+        <v>261</v>
+      </c>
+      <c r="K24" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" t="s">
+        <v>267</v>
+      </c>
+      <c r="F25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G25" t="s">
+        <v>269</v>
+      </c>
+      <c r="H25" t="s">
+        <v>270</v>
+      </c>
+      <c r="I25" t="s">
+        <v>271</v>
+      </c>
+      <c r="J25" t="s">
+        <v>272</v>
+      </c>
+      <c r="K25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" t="s">
+        <v>277</v>
+      </c>
+      <c r="F26" t="s">
+        <v>278</v>
+      </c>
+      <c r="G26" t="s">
+        <v>279</v>
+      </c>
+      <c r="H26" t="s">
+        <v>280</v>
+      </c>
+      <c r="I26" t="s">
+        <v>281</v>
+      </c>
+      <c r="J26" t="s">
+        <v>282</v>
+      </c>
+      <c r="K26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E27" t="s">
+        <v>288</v>
+      </c>
+      <c r="F27" t="s">
+        <v>289</v>
+      </c>
+      <c r="G27" t="s">
+        <v>290</v>
+      </c>
+      <c r="H27" t="s">
+        <v>291</v>
+      </c>
+      <c r="I27" t="s">
+        <v>292</v>
+      </c>
+      <c r="J27" t="s">
+        <v>293</v>
+      </c>
+      <c r="K27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>295</v>
+      </c>
+      <c r="B28" t="s">
+        <v>296</v>
+      </c>
+      <c r="C28" t="s">
+        <v>297</v>
+      </c>
+      <c r="D28" t="s">
+        <v>298</v>
+      </c>
+      <c r="E28" t="s">
+        <v>299</v>
+      </c>
+      <c r="F28" t="s">
+        <v>300</v>
+      </c>
+      <c r="G28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H28" t="s">
+        <v>302</v>
+      </c>
+      <c r="I28" t="s">
+        <v>303</v>
+      </c>
+      <c r="J28" t="s">
+        <v>304</v>
+      </c>
+      <c r="K28" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" t="s">
+        <v>308</v>
+      </c>
+      <c r="D29" t="s">
+        <v>309</v>
+      </c>
+      <c r="E29" t="s">
+        <v>310</v>
+      </c>
+      <c r="F29" t="s">
+        <v>311</v>
+      </c>
+      <c r="G29" t="s">
+        <v>312</v>
+      </c>
+      <c r="H29" t="s">
+        <v>313</v>
+      </c>
+      <c r="I29" t="s">
+        <v>314</v>
+      </c>
+      <c r="J29" t="s">
+        <v>315</v>
+      </c>
+      <c r="K29" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>317</v>
+      </c>
+      <c r="B30" t="s">
+        <v>318</v>
+      </c>
+      <c r="C30" t="s">
+        <v>319</v>
+      </c>
+      <c r="D30" t="s">
+        <v>320</v>
+      </c>
+      <c r="E30" t="s">
+        <v>321</v>
+      </c>
+      <c r="F30" t="s">
+        <v>322</v>
+      </c>
+      <c r="G30" t="s">
+        <v>323</v>
+      </c>
+      <c r="H30" t="s">
+        <v>324</v>
+      </c>
+      <c r="I30" t="s">
+        <v>325</v>
+      </c>
+      <c r="J30" t="s">
+        <v>326</v>
+      </c>
+      <c r="K30" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>328</v>
+      </c>
+      <c r="B31" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" t="s">
+        <v>330</v>
+      </c>
+      <c r="D31" t="s">
+        <v>331</v>
+      </c>
+      <c r="E31" t="s">
+        <v>332</v>
+      </c>
+      <c r="F31" t="s">
+        <v>333</v>
+      </c>
+      <c r="G31" t="s">
+        <v>334</v>
+      </c>
+      <c r="H31" t="s">
+        <v>335</v>
+      </c>
+      <c r="I31" t="s">
+        <v>336</v>
+      </c>
+      <c r="J31" t="s">
+        <v>337</v>
+      </c>
+      <c r="K31" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B32" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32" t="s">
+        <v>341</v>
+      </c>
+      <c r="D32" t="s">
+        <v>342</v>
+      </c>
+      <c r="E32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" t="s">
+        <v>344</v>
+      </c>
+      <c r="G32" t="s">
+        <v>345</v>
+      </c>
+      <c r="H32" t="s">
+        <v>346</v>
+      </c>
+      <c r="I32" t="s">
+        <v>347</v>
+      </c>
+      <c r="J32" t="s">
+        <v>348</v>
+      </c>
+      <c r="K32" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>350</v>
+      </c>
+      <c r="B33" t="s">
+        <v>351</v>
+      </c>
+      <c r="C33" t="s">
+        <v>352</v>
+      </c>
+      <c r="D33" t="s">
+        <v>353</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>354</v>
+      </c>
+      <c r="G33" t="s">
+        <v>355</v>
+      </c>
+      <c r="H33" t="s">
+        <v>356</v>
+      </c>
+      <c r="I33" t="s">
+        <v>357</v>
+      </c>
+      <c r="J33" t="s">
+        <v>358</v>
+      </c>
+      <c r="K33" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>360</v>
+      </c>
+      <c r="B34" t="s">
+        <v>361</v>
+      </c>
+      <c r="C34" t="s">
+        <v>362</v>
+      </c>
+      <c r="D34" t="s">
+        <v>363</v>
+      </c>
+      <c r="E34" t="s">
+        <v>364</v>
+      </c>
+      <c r="F34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G34" t="s">
+        <v>366</v>
+      </c>
+      <c r="H34" t="s">
+        <v>367</v>
+      </c>
+      <c r="I34" t="s">
+        <v>368</v>
+      </c>
+      <c r="J34" t="s">
+        <v>369</v>
+      </c>
+      <c r="K34" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>371</v>
+      </c>
+      <c r="B35" t="s">
+        <v>372</v>
+      </c>
+      <c r="C35" t="s">
+        <v>373</v>
+      </c>
+      <c r="D35" t="s">
+        <v>374</v>
+      </c>
+      <c r="E35" t="s">
+        <v>375</v>
+      </c>
+      <c r="F35" t="s">
+        <v>376</v>
+      </c>
+      <c r="G35" t="s">
+        <v>377</v>
+      </c>
+      <c r="H35" t="s">
+        <v>378</v>
+      </c>
+      <c r="I35" t="s">
+        <v>379</v>
+      </c>
+      <c r="J35" t="s">
+        <v>380</v>
+      </c>
+      <c r="K35" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" t="s">
+        <v>383</v>
+      </c>
+      <c r="C36" t="s">
+        <v>384</v>
+      </c>
+      <c r="D36" t="s">
+        <v>385</v>
+      </c>
+      <c r="E36" t="s">
+        <v>386</v>
+      </c>
+      <c r="F36" t="s">
+        <v>387</v>
+      </c>
+      <c r="G36" t="s">
+        <v>388</v>
+      </c>
+      <c r="H36" t="s">
+        <v>389</v>
+      </c>
+      <c r="I36" t="s">
+        <v>390</v>
+      </c>
+      <c r="J36" t="s">
+        <v>391</v>
+      </c>
+      <c r="K36" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>393</v>
+      </c>
+      <c r="B37" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" t="s">
+        <v>396</v>
+      </c>
+      <c r="E37" t="s">
+        <v>397</v>
+      </c>
+      <c r="F37" t="s">
+        <v>398</v>
+      </c>
+      <c r="G37" t="s">
+        <v>399</v>
+      </c>
+      <c r="H37" t="s">
+        <v>400</v>
+      </c>
+      <c r="I37" t="s">
+        <v>401</v>
+      </c>
+      <c r="J37" t="s">
+        <v>402</v>
+      </c>
+      <c r="K37" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>404</v>
+      </c>
+      <c r="B38" t="s">
+        <v>405</v>
+      </c>
+      <c r="C38" t="s">
+        <v>406</v>
+      </c>
+      <c r="D38" t="s">
+        <v>407</v>
+      </c>
+      <c r="E38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F38" t="s">
+        <v>409</v>
+      </c>
+      <c r="G38" t="s">
+        <v>410</v>
+      </c>
+      <c r="H38" t="s">
+        <v>411</v>
+      </c>
+      <c r="I38" t="s">
+        <v>412</v>
+      </c>
+      <c r="J38" t="s">
+        <v>413</v>
+      </c>
+      <c r="K38" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>415</v>
+      </c>
+      <c r="B39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C39" t="s">
+        <v>417</v>
+      </c>
+      <c r="D39" t="s">
+        <v>418</v>
+      </c>
+      <c r="E39" t="s">
+        <v>419</v>
+      </c>
+      <c r="F39" t="s">
+        <v>420</v>
+      </c>
+      <c r="G39" t="s">
+        <v>421</v>
+      </c>
+      <c r="H39" t="s">
+        <v>422</v>
+      </c>
+      <c r="I39" t="s">
+        <v>423</v>
+      </c>
+      <c r="J39" t="s">
+        <v>424</v>
+      </c>
+      <c r="K39" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>426</v>
+      </c>
+      <c r="B40" t="s">
+        <v>427</v>
+      </c>
+      <c r="C40" t="s">
+        <v>428</v>
+      </c>
+      <c r="D40" t="s">
+        <v>429</v>
+      </c>
+      <c r="E40" t="s">
+        <v>430</v>
+      </c>
+      <c r="F40" t="s">
+        <v>431</v>
+      </c>
+      <c r="G40" t="s">
+        <v>432</v>
+      </c>
+      <c r="H40" t="s">
+        <v>433</v>
+      </c>
+      <c r="I40" t="s">
+        <v>434</v>
+      </c>
+      <c r="J40" t="s">
+        <v>435</v>
+      </c>
+      <c r="K40" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>437</v>
+      </c>
+      <c r="B41" t="s">
+        <v>438</v>
+      </c>
+      <c r="C41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D41" t="s">
+        <v>440</v>
+      </c>
+      <c r="E41" t="s">
+        <v>441</v>
+      </c>
+      <c r="F41" t="s">
+        <v>442</v>
+      </c>
+      <c r="G41" t="s">
+        <v>443</v>
+      </c>
+      <c r="H41" t="s">
+        <v>444</v>
+      </c>
+      <c r="I41" t="s">
+        <v>445</v>
+      </c>
+      <c r="J41" t="s">
+        <v>446</v>
+      </c>
+      <c r="K41" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>448</v>
+      </c>
+      <c r="B42" t="s">
+        <v>449</v>
+      </c>
+      <c r="C42" t="s">
+        <v>450</v>
+      </c>
+      <c r="D42" t="s">
+        <v>451</v>
+      </c>
+      <c r="E42" t="s">
+        <v>452</v>
+      </c>
+      <c r="F42" t="s">
+        <v>453</v>
+      </c>
+      <c r="G42" t="s">
+        <v>454</v>
+      </c>
+      <c r="H42" t="s">
+        <v>455</v>
+      </c>
+      <c r="I42" t="s">
+        <v>456</v>
+      </c>
+      <c r="J42" t="s">
+        <v>457</v>
+      </c>
+      <c r="K42" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>459</v>
+      </c>
+      <c r="B43" t="s">
+        <v>460</v>
+      </c>
+      <c r="C43" t="s">
+        <v>461</v>
+      </c>
+      <c r="D43" t="s">
+        <v>462</v>
+      </c>
+      <c r="E43" t="s">
+        <v>463</v>
+      </c>
+      <c r="F43" t="s">
+        <v>464</v>
+      </c>
+      <c r="G43" t="s">
+        <v>465</v>
+      </c>
+      <c r="H43" t="s">
+        <v>466</v>
+      </c>
+      <c r="I43" t="s">
+        <v>467</v>
+      </c>
+      <c r="J43" t="s">
+        <v>468</v>
+      </c>
+      <c r="K43" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>470</v>
+      </c>
+      <c r="B44" t="s">
+        <v>471</v>
+      </c>
+      <c r="C44" t="s">
+        <v>472</v>
+      </c>
+      <c r="D44" t="s">
+        <v>473</v>
+      </c>
+      <c r="E44" t="s">
+        <v>474</v>
+      </c>
+      <c r="F44" t="s">
+        <v>475</v>
+      </c>
+      <c r="G44" t="s">
+        <v>476</v>
+      </c>
+      <c r="H44" t="s">
+        <v>477</v>
+      </c>
+      <c r="I44" t="s">
+        <v>478</v>
+      </c>
+      <c r="J44" t="s">
+        <v>479</v>
+      </c>
+      <c r="K44" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>481</v>
+      </c>
+      <c r="B45" t="s">
+        <v>482</v>
+      </c>
+      <c r="C45" t="s">
+        <v>483</v>
+      </c>
+      <c r="D45" t="s">
+        <v>484</v>
+      </c>
+      <c r="E45" t="s">
+        <v>485</v>
+      </c>
+      <c r="F45" t="s">
+        <v>486</v>
+      </c>
+      <c r="G45" t="s">
+        <v>487</v>
+      </c>
+      <c r="H45" t="s">
+        <v>488</v>
+      </c>
+      <c r="I45" t="s">
+        <v>489</v>
+      </c>
+      <c r="J45" t="s">
+        <v>490</v>
+      </c>
+      <c r="K45" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>492</v>
+      </c>
+      <c r="B46" t="s">
+        <v>493</v>
+      </c>
+      <c r="C46" t="s">
+        <v>494</v>
+      </c>
+      <c r="D46" t="s">
+        <v>495</v>
+      </c>
+      <c r="E46" t="s">
+        <v>496</v>
+      </c>
+      <c r="F46" t="s">
+        <v>497</v>
+      </c>
+      <c r="G46" t="s">
+        <v>498</v>
+      </c>
+      <c r="H46" t="s">
+        <v>499</v>
+      </c>
+      <c r="I46" t="s">
+        <v>500</v>
+      </c>
+      <c r="J46" t="s">
+        <v>501</v>
+      </c>
+      <c r="K46" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>503</v>
+      </c>
+      <c r="B47" t="s">
+        <v>504</v>
+      </c>
+      <c r="C47" t="s">
+        <v>505</v>
+      </c>
+      <c r="D47" t="s">
+        <v>506</v>
+      </c>
+      <c r="E47" t="s">
+        <v>507</v>
+      </c>
+      <c r="F47" t="s">
+        <v>508</v>
+      </c>
+      <c r="G47" t="s">
+        <v>509</v>
+      </c>
+      <c r="H47" t="s">
+        <v>510</v>
+      </c>
+      <c r="I47" t="s">
+        <v>511</v>
+      </c>
+      <c r="J47" t="s">
+        <v>512</v>
+      </c>
+      <c r="K47" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>514</v>
+      </c>
+      <c r="B48" t="s">
+        <v>515</v>
+      </c>
+      <c r="C48" t="s">
+        <v>516</v>
+      </c>
+      <c r="D48" t="s">
+        <v>517</v>
+      </c>
+      <c r="E48" t="s">
+        <v>518</v>
+      </c>
+      <c r="F48" t="s">
+        <v>519</v>
+      </c>
+      <c r="G48" t="s">
+        <v>520</v>
+      </c>
+      <c r="H48" t="s">
+        <v>521</v>
+      </c>
+      <c r="I48" t="s">
+        <v>522</v>
+      </c>
+      <c r="J48" t="s">
+        <v>523</v>
+      </c>
+      <c r="K48" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>525</v>
+      </c>
+      <c r="B49" t="s">
+        <v>526</v>
+      </c>
+      <c r="C49" t="s">
+        <v>527</v>
+      </c>
+      <c r="D49" t="s">
+        <v>528</v>
+      </c>
+      <c r="E49" t="s">
+        <v>529</v>
+      </c>
+      <c r="F49" t="s">
+        <v>530</v>
+      </c>
+      <c r="G49" t="s">
+        <v>531</v>
+      </c>
+      <c r="H49" t="s">
+        <v>532</v>
+      </c>
+      <c r="I49" t="s">
+        <v>533</v>
+      </c>
+      <c r="J49" t="s">
+        <v>534</v>
+      </c>
+      <c r="K49" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>536</v>
+      </c>
+      <c r="B50" t="s">
+        <v>537</v>
+      </c>
+      <c r="C50" t="s">
+        <v>538</v>
+      </c>
+      <c r="D50" t="s">
+        <v>539</v>
+      </c>
+      <c r="E50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" t="s">
+        <v>540</v>
+      </c>
+      <c r="G50" t="s">
+        <v>541</v>
+      </c>
+      <c r="H50" t="s">
+        <v>542</v>
+      </c>
+      <c r="I50" t="s">
+        <v>543</v>
+      </c>
+      <c r="J50" t="s">
+        <v>544</v>
+      </c>
+      <c r="K50" t="s">
+        <v>545</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>